--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -413,20 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -437,217 +439,2676 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Property Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Bedrooms</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Bathrooms</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Size (sqft)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>Listing URL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Listed Date</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Days Listed</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Raw Card Text</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped At</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Autos</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Condominium For Sale
+listed 2 weeks ago
+RM 550,000
+Tri Pinnacle, Tanjong Tokong
+800
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+TRI Pinnacle</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RM 550,000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/tri-pinnacle-114681845.htm</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 550,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI Pinnacle</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Apartment For Sale
+listed 2 weeks ago
+RM 240,000
+Puncak Erskine, Tanjong Tokong
+600
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+Puncak Erskine Apartment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RM 240,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/puncak-erskine-apartment-114957457.htm</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Apartment For Sale | listed 2 weeks ago | RM 240,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Puncak Erskine Apartment</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 2 weeks ago
+RM 638,000
+The Peak Residences, Tanjong Tokong
+1,100
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+The Peak Resident Condominium</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RM 638,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/the-peak-resident-condominium-114960623.htm</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 638,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Resident Condominium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Shop lot For Sale
+listed 2 weeks ago
+RM 689,000
+Tanjong Tokong, Penang
+930
+sq.ft
+Freehold
+Island 88 Shoplot (1st Floor)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RM 689,000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/island-88-shoplot-1st-floor-114982296.htm</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Shop lot For Sale | listed 2 weeks ago | RM 689,000 | Tanjong Tokong, Penang |  | 930 |  | sq.ft |  | Freehold |  | Island 88 Shoplot (1st Floor)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.5-storey Terraced House For Sale
+listed 2 weeks ago
+RM 899,000
+Tanjong Tokong, Penang
+1,900
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RM 899,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tanjung Tokong</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/1-5-storey-terraced-house-tanjung-tokong-near-straight-quay-gurney-114981119.htm</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>14</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.5-storey Terraced House For Sale | listed 2 weeks ago | RM 899,000 | Tanjong Tokong, Penang |  | 1,900 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | 1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Apartment For Sale
+listed 2 weeks ago
+RM 180,000
+Puncak Erskine, Tanjong Tokong
+650
+sq.ft
+3
+Bed
+3
+Bath
+Freehold
+Puncak Erskine 88 Full Furnished &amp; Renovated</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RM 180,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/puncak-erskine-88-full-furnished-renovated-115022482.htm</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Apartment For Sale | listed 2 weeks ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Puncak Erskine 88 Full Furnished &amp; Renovated</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 2 weeks ago
+RM 380,000
+Twin Towers, Tanjung Bungah
+926
+sq.ft
+2
+Bed
+2
+Bath
+Freehold
+Furnished with nice seaview</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RM 380,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/furnished-with-nice-seaview-114995729.htm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 380,000 | Twin Towers, Tanjung Bungah |  | 926 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Furnished with nice seaview</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 2 weeks ago
+RM 415,000
+Tri Pinnacle, Tanjong Tokong
+800
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RM 415,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/tri-pinnacle-condo-tanjong-tokong-800sf-for-sale-original-unit-114993450.htm</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>14</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 415,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 2 weeks ago
+RM 565,000
+Twin Towers, Tanjung Bungah
+1,248
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+Twin Tower Condo Tanjung Bunga</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RM 565,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/twin-tower-condo-tanjung-bunga-114995728.htm</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>14</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 565,000 | Twin Towers, Tanjung Bungah |  | 1,248 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Tower Condo Tanjung Bunga</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 2 weeks ago
+RM 1,227,000
+City Of Dreams, Tanjong Tokong
+1,185
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+City of Dreams Seaview Condo 1185sf Fully Furnished</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RM 1,227,000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1185</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/city-of-dreams-seaview-condo-1185sf-fully-furnished-115000031.htm</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>14</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 1,227,000 | City Of Dreams, Tanjong Tokong |  | 1,185 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | City of Dreams Seaview Condo 1185sf Fully Furnished</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Apartment For Sale
+listed 1 week ago
+RM 530,000
+Skyridge Apartment, Tanjong Tokong
+850
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+Taman Skyridge Apartment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RM 530,000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/taman-skyridge-apartment-115060516.htm</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Apartment For Sale | listed 1 week ago | RM 530,000 | Skyridge Apartment, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Taman Skyridge Apartment</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 1 week ago
+RM 450,000
+Tri Pinnacle, Tanjong Tokong
+800
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+tri pinnacle tanjung tokong</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RM 450,000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tanjung Tokong</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-115045263.htm</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 1 week ago | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 1 week ago
+RM 600,000
+Twin Towers, Tanjung Bungah
+1,300
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+Twin Towers Condo, Tg Bungah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RM 600,000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/twin-towers-condo-tg-bungah-115027655.htm</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 1 week ago | RM 600,000 | Twin Towers, Tanjung Bungah |  | 1,300 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Towers Condo, Tg Bungah</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 1 week ago
+RM 799,000
+The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong
+1,047
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+The Tamarind, walking distance to Stonyhurst International School</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RM 799,000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/the-tamarind-walking-distance-to-stonyhurst-international-school-115026766.htm</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 1 week ago | RM 799,000 | The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong |  | 1,047 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Tamarind, walking distance to Stonyhurst International School</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Townhouse For Sale
+listed 1 week ago
+RM 580,000
+Tanjung Bungah, Penang
+1,000
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+Quiet Townhouse with Seaview</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RM 580,000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/quiet-townhouse-with-seaview-115045058.htm</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Townhouse For Sale | listed 1 week ago | RM 580,000 | Tanjung Bungah, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Quiet Townhouse with Seaview</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 1 week ago
+RM 530,000
+I-Santorini, Tanjong Tokong
+1,000
+sq.ft
+3
+Bed
+2
+Bath
+Leasehold
+Santorini renovated</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RM 530,000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/santorini-renovated-115045187.htm</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 1 week ago | RM 530,000 | I-Santorini, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Santorini renovated</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 1 week ago
+RM 3,300,000
+One Tanjong, Tanjung Bungah
+4,756
+sq.ft
+5
+Bed
+5
+Bath
+Freehold
+Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>RM 3,300,000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4756</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/luxury-apartment-with-unobstructed-sea-view-best-price-on-the-market-115022080.htm</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 1 week ago | RM 3,300,000 | One Tanjong, Tanjung Bungah |  | 4,756 |  | sq.ft |  | 5 |  | Bed |  | 5 |  | Bath |  | Freehold |  | Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 6 days ago
+RM 4,800,000
+Springtide Residences, Tanjung Bungah
+5,221
+sq.ft
+5
+Bed
+7
+Bath
+Freehold
+Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RM 4,800,000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>5221</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/springtide-residences-beachfront-luxury-condominium-in-tanjung-bungah-115100943.htm</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 6 days ago | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 4 days ago
+RM 608,000
+I-Santorini, Tanjong Tokong
+800
+sq.ft
+3
+Bed
+2
+Bath
+Leasehold
+3 bedrooms 2 bathrooms 2 car park</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>RM 608,000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/3-bedrooms-2-bathrooms-2-car-park-for-sale-115083940.htm</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 4 days ago | RM 608,000 | I-Santorini, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | 3 bedrooms 2 bathrooms 2 car park for sale</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Apartment For Sale
+listed 4 days ago
+RM 299,950
+Taman Kristal, Tanjong Tokong
+700
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+An airy and pleasant unit on the top most floor with scenic views</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>RM 299,950</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/an-airy-and-pleasant-unit-on-the-top-most-floor-with-scenic-views-114303816.htm</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Apartment For Sale | listed 4 days ago | RM 299,950 | Taman Kristal, Tanjong Tokong |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | An airy and pleasant unit on the top most floor with scenic views</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Apartment For Sale
+listed 4 days ago
+RM 340,000
+Tri Pinnacle, Tanjong Tokong
+650
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+Below Market Attractive Unit</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RM 340,000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/below-market-attractive-unit-115034831.htm</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Apartment For Sale | listed 4 days ago | RM 340,000 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Below Market Attractive Unit</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Apartment For Sale
+listed 3 days ago
+RM 342,000
+E Garden, Tanjong Tokong
+760
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+E Garden apartment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RM 342,000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/e-garden-apartment-for-sale-115127752.htm</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Apartment For Sale | listed 3 days ago | RM 342,000 | E Garden, Tanjong Tokong |  | 760 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | E Garden apartment for sale</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Service Residence For Sale
+listed 3 days ago
+RM 2,500,000
+Straits Quay, Tanjong Tokong
+1,296
+sq.ft
+2
+Bed
+3
+Bath
+Freehold
+Straits Residence one of the best Investment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RM 2,500,000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/straits-residence-one-of-the-best-investment-115089396.htm</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Service Residence For Sale | listed 3 days ago | RM 2,500,000 | Straits Quay, Tanjong Tokong |  | 1,296 |  | sq.ft |  | 2 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Straits Residence one of the best Investment</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Apartment For Sale
+listed 3 days ago
+RM 180,000
+Puncak Erskine, Tanjong Tokong
+600
+sq.ft
+3
+Bed
+1
+Bath
+Freehold
+Apartment</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RM 180,000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/apartment-for-sale-115093031.htm</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Apartment For Sale | listed 3 days ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 1 |  | Bath |  | Freehold |  | Apartment For Sale</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 3 days ago
+RM 530,000
+The Peak Residences, Tanjong Tokong
+1,100
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+The Peak Condominium</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>RM 530,000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/the-peak-condominium-115093455.htm</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 3 days ago | RM 530,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Condominium</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 3 days ago
+RM 538,000
+I-Santorini, Tanjong Tokong
+850
+sq.ft
+3
+Bed
+2
+Bath
+Leasehold
+Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>RM 538,000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/direct-owner-fully-furnished-nice-santorini-with-3-carparks-115127587.htm</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 3 days ago | RM 538,000 | I-Santorini, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Semi-Detached House For Sale
+listed 3 days ago
+RM 1,650,000
+Tanjung Bungah, Penang
+4,395
+sq.ft
+4
+Bed
+2
+Bath
+Freehold
+Single Storey Semi D House Hillside,Tanjung Bungah,Penang.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>RM 1,650,000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>4395</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/single-storey-semi-d-house-hillside-tanjung-bungah-penang-113480651.htm</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Semi-Detached House For Sale | listed 3 days ago | RM 1,650,000 | Tanjung Bungah, Penang |  | 4,395 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Single Storey Semi D House Hillside,Tanjung Bungah,Penang.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 3 days ago
+RM 528,000
+The Peak Residences, Tanjong Tokong
+1,000
+sq.ft
+2
+Bed
+2
+Bath
+Freehold
+The peak RENO to TWO room</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>RM 528,000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/the-peak-reno-to-two-room-115092789.htm</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 3 days ago | RM 528,000 | The Peak Residences, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The peak RENO to TWO room</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 3 days ago
+RM 500,000
+Tri Pinnacle, Tanjong Tokong
+850
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>RM 500,000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Tanjung Tokong</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-jalan-persiaran-halia-3-tanjung-tokong-115090201.htm</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 3 days ago | RM 500,000 | Tri Pinnacle, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Townhouse For Sale
+listed 3 days ago
+RM 760,000
+Tanjung Bungah, Penang
+1,200
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+House</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>RM 760,000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/house-for-sale-108064933.htm</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Townhouse For Sale | listed 3 days ago | RM 760,000 | Tanjung Bungah, Penang |  | 1,200 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | House for sale</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1-storey Terraced House For Sale
+listed 3 days ago
+RM 410,000
+Tanjong Tokong, Penang
+1,000
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>RM 410,000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/taman-intan-delima-single-storey-terrace-batu-kawan-freehold-115126865.htm</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1-storey Terraced House For Sale | listed 3 days ago | RM 410,000 | Tanjong Tokong, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 2 days ago
+RM 1,200,000
+Quayside, Tanjong Tokong
+1,137
+sq.ft
+1
+Bed
+2
+Bath
+Freehold
+Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>RM 1,200,000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1137</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/pinang-quayside-condo-fully-furnished-1bedroom-2-bathrooms-unit-103758517.htm</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 days ago | RM 1,200,000 | Quayside, Tanjong Tokong |  | 1,137 |  | sq.ft |  | 1 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 2 days ago
+RM 368,000
+5%
+RM 388,000
+Hillside Garden, Tanjung Bungah
+700
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+Tanjong Bungah Hillside Garden Apartment For Sale.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>RM 368,000</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/tanjong-bungah-hillside-garden-apartment-for-sale-114853211.htm</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 days ago | RM 368,000 | 5% | RM 388,000 | Hillside Garden, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tanjong Bungah Hillside Garden Apartment For Sale.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 2 days ago
+RM 600,000
+Marine Mansion, Tanjung Bungah
+850
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+Marine Mansion</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>RM 600,000</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/marine-mansion-115137839.htm</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 days ago | RM 600,000 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Marine Mansion</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 2 days ago
+RM 353,800
+Tri Pinnacle, Tanjong Tokong
+650
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>RM 353,800</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/tg-tokong-apartment-fully-furnished-with-2-carparks-115129412.htm</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 days ago | RM 353,800 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 23 hours ago
+RM 335,000
+Azuria, Tanjung Bungah
+700
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+Azuria Condominium - Direct Owner</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>RM 335,000</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/azuria-condominium-direct-owner-111620926.htm</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 23 hours ago | RM 335,000 | Azuria, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Azuria Condominium - Direct Owner</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 1 hour ago
+RM 15,933,500
+City Of Dreams, Tanjong Tokong
+1,500
+sq.ft
+4
+Bed
+2
+Bath
+Freehold
+city of dream condominiums house gurney sea view</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>RM 15,933,500</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/city-of-dream-condominiums-house-gurney-sea-view-115155857.htm</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 1 hour ago | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 2 hours ago
+RM 598,888
+Marine Mansion, Tanjung Bungah
+850
+sq.ft
+4
+Bed
+2
+Bath
+Freehold
+Looking For Investors Only</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>RM 598,888</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Tanjung Bungah</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.mudah.my</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/looking-for-investors-only-115155444.htm</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Autos |  | Property |  | Electronics |  | Jobs &amp; Services |  | All Categories |  | Help Center |  | Pro Niaga |  | Get App |  | POST FREE AD |  | Mudah.my | Property for Sale | Properties for Sale in Malaysia | ▼ | Buy | Rent | Apartment Directory | 5 Locations Selected | Minden Heights, PNG | +4 Locations | SEARCH | All Properties | More filters |  | Video Ads Are Here |  | Giving you a clearer view of the property's condition before enquiring. |  | Try It Now | 117 results found: All Properties For Sale in Minden Heights, Persiaran Gurney, Pulau Tikus, Tanjong Tokong and Tanjung Bungah | All (2,299) | By Owner (117) | By Agents (2,182) | SORT | Condominium For Sale | listed 1 hour ago | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view |  | by | Private advertiser | Condominium For Sale | listed 2 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only |  | by | Private advertiser | Condominium For Sale | listed 2 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only |  | by | Private advertiser | Apartment For Sale | listed 22 hours ago | RM 360,000 | Skyridge Apartment, Tanjong Tokong |  | 750 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | [RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney |  | by | Private advertiser | Condominium For Sale | listed 22 hours ago | RM 335,000 | Azuria, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Azuria Condominium - Direct Owner |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 600,000 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Marine Mansion |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 1,200,000 | Quayside, Tanjong Tokong |  | 1,137 |  | sq.ft |  | 1 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 368,000 | 5% | RM 388,000 | Hillside Garden, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tanjong Bungah Hillside Garden Apartment For Sale. |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 353,800 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tg Tokong Apartment - Fully Furnished with 2 carparks |  | by | Private advertiser | Semi-Detached House For Sale | listed 3 days ago | RM 1,650,000 | Tanjung Bungah, Penang |  | 4,395 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Single Storey Semi D House Hillside,Tanjung Bungah,Penang. |  | by | Private advertiser | Apartment For Sale | listed 3 days ago | RM 342,000 | E Garden, Tanjong Tokong |  | 760 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | E Garden apartment for sale |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 538,000 | I-Santorini, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Direct Owner Fully Furnished Nice Santorini with 3 carparks |  | by | Private advertiser | 1-storey Terraced House For Sale | listed 3 days ago | RM 410,000 | Tanjong Tokong, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold |  | by | Private advertiser | Townhouse For Sale | listed 3 days ago | RM 760,000 | Tanjung Bungah, Penang |  | 1,200 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | House for sale |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 530,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Condominium |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 500,000 | Tri Pinnacle, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong, |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 528,000 | The Peak Residences, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The peak RENO to TWO room |  | by | Private advertiser | Apartment For Sale | listed 3 days ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 1 |  | Bath |  | Freehold |  | Apartment For Sale |  | by | Private advertiser | Service Residence For Sale | listed 3 days ago | RM 2,500,000 | Straits Quay, Tanjong Tokong |  | 1,296 |  | sq.ft |  | 2 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Straits Residence one of the best Investment |  | by | Private advertiser | Condominium For Sale | listed 4 days ago | RM 608,000 | I-Santorini, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | 3 bedrooms 2 bathrooms 2 car park for sale |  | by | Private advertiser | Apartment For Sale | listed 4 days ago | RM 340,000 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Below Market Attractive Unit |  | by | Private advertiser | Apartment For Sale | listed 4 days ago | RM 299,950 | Taman Kristal, Tanjong Tokong |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | An airy and pleasant unit on the top most floor with scenic views |  | by | Private advertiser | Condominium For Sale | listed 6 days ago | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah |  | by | Private advertiser | Apartment For Sale | listed 1 week ago | RM 530,000 | Skyridge Apartment, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Taman Skyridge Apartment |  | by | Private advertiser | Townhouse For Sale | listed 1 week ago | RM 580,000 | Tanjung Bungah, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Quiet Townhouse with Seaview |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 530,000 | I-Santorini, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Santorini renovated |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 3,300,000 | One Tanjong, Tanjung Bungah |  | 4,756 |  | sq.ft |  | 5 |  | Bed |  | 5 |  | Bath |  | Freehold |  | Luxury Apartment with Unobstructed Sea View – Best Price on the Market |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 799,000 | The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong |  | 1,047 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Tamarind, walking distance to Stonyhurst International School |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 600,000 | Twin Towers, Tanjung Bungah |  | 1,300 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Towers Condo, Tg Bungah |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 1,227,000 | City Of Dreams, Tanjong Tokong |  | 1,185 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | City of Dreams Seaview Condo 1185sf Fully Furnished |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 565,000 | Twin Towers, Tanjung Bungah |  | 1,248 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Tower Condo Tanjung Bunga |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 415,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 380,000 | Twin Towers, Tanjung Bungah |  | 926 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Furnished with nice seaview |  | by | Private advertiser | Apartment For Sale | listed 2 weeks ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Puncak Erskine 88 Full Furnished &amp; Renovated |  | by | Private advertiser | 1.5-storey Terraced House For Sale | listed 2 weeks ago | RM 899,000 | Tanjong Tokong, Penang |  | 1,900 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | 1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney |  | by | Private advertiser | Shop lot For Sale | listed 2 weeks ago | RM 689,000 | Tanjong Tokong, Penang |  | 930 |  | sq.ft |  | Freehold |  | Island 88 Shoplot (1st Floor) |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 638,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Resident Condominium |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 550,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI Pinnacle |  | by | Private advertiser | Apartment For Sale | listed 2 weeks ago | RM 240,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Puncak Erskine Apartment |  | by | Private advertiser | 1 | 2 | 3 | Explore More on Mudah | selangor | corner | puchong | ampang | kajang | klang | shah alam | corner lot | cyberjaya | cheras | toyota wish | nissan x-trail hybrid | auto selection | parkview towers | mercedes s580e | milano eight kuching | harga x adv 750 second | pangsapuri laksamana batu caves | hulu langat | pangsapuri setia impian |  | ADVERTISEMENT |  | SAVE SEARCH | Popular Locations in Malaysia | Selangor | Penang | Johor | Show More | Popular Property Type in Malaysia | Apartments | Houses | Commercial Properties | Show More | Popular Properties by Budget in Malaysia | Under RM 200 K | Under RM 300 K | Under RM 400 K | Show More | Popular Properties by Bedrooms in Malaysia | 1 Bedroom in Apartments | 2 Bedrooms in Apartments | 3 Bedrooms in Apartments | Show More |  | ADVERTISEMENT |  | About Us | Rules | Post Free Ad | Shop Safely | Banner Advertising | Contact Us | Help Center | Careers | Terms | Privacy | Business Conduct | © Mudah.my Sdn Bhd</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-07-02 05:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Mudah.my</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>RM 15,933,500</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Tanjung Bungah</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.mudah.my/</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Condominium For Sale
+listed 2 hours ago
+RM 888,888
+Desa Mas (Pulau Tikus), Pulau Tikus
+1,089
+sq.ft
+5
+Bed
+2
+Bath
+Freehold
+Looking For Investors Only</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>RM 888,888</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pulau Tikus</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/looking-for-investors-only-115155435.htm</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Mudah.my | Property for Sale | Properties for Sale in Malaysia | ▼ | Buy | Rent | Apartment Directory | 5 Locations Selected | Minden Heights, PNG | +4 Locations | SEARCH | All Properties | More filters |  | Video Ads Are Here |  | Giving you a clearer view of the property's condition before enquiring. |  | Try It Now | 117 results found: All Properties For Sale in Minden Heights, Persiaran Gurney, Pulau Tikus, Tanjong Tokong and Tanjung Bungah | All (2,299) | By Owner (117) | By Agents (2,182) | SORT | Condominium For Sale | listed 1 hour ago | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view |  | by | Private advertiser | Condominium For Sale | listed 2 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only |  | by | Private advertiser | Condominium For Sale | listed 2 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only |  | by | Private advertiser | Apartment For Sale | listed 22 hours ago | RM 360,000 | Skyridge Apartment, Tanjong Tokong |  | 750 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | [RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney |  | by | Private advertiser | Condominium For Sale | listed 22 hours ago | RM 335,000 | Azuria, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Azuria Condominium - Direct Owner |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 600,000 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Marine Mansion |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 1,200,000 | Quayside, Tanjong Tokong |  | 1,137 |  | sq.ft |  | 1 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 368,000 | 5% | RM 388,000 | Hillside Garden, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tanjong Bungah Hillside Garden Apartment For Sale. |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 353,800 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tg Tokong Apartment - Fully Furnished with 2 carparks |  | by | Private advertiser | Semi-Detached House For Sale | listed 3 days ago | RM 1,650,000 | Tanjung Bungah, Penang |  | 4,395 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Single Storey Semi D House Hillside,Tanjung Bungah,Penang. |  | by | Private advertiser | Apartment For Sale | listed 3 days ago | RM 342,000 | E Garden, Tanjong Tokong |  | 760 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | E Garden apartment for sale |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 538,000 | I-Santorini, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Direct Owner Fully Furnished Nice Santorini with 3 carparks |  | by | Private advertiser | 1-storey Terraced House For Sale | listed 3 days ago | RM 410,000 | Tanjong Tokong, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold |  | by | Private advertiser | Townhouse For Sale | listed 3 days ago | RM 760,000 | Tanjung Bungah, Penang |  | 1,200 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | House for sale |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 530,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Condominium |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 500,000 | Tri Pinnacle, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong, |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 528,000 | The Peak Residences, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The peak RENO to TWO room |  | by | Private advertiser | Apartment For Sale | listed 3 days ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 1 |  | Bath |  | Freehold |  | Apartment For Sale |  | by | Private advertiser | Service Residence For Sale | listed 3 days ago | RM 2,500,000 | Straits Quay, Tanjong Tokong |  | 1,296 |  | sq.ft |  | 2 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Straits Residence one of the best Investment |  | by | Private advertiser | Condominium For Sale | listed 4 days ago | RM 608,000 | I-Santorini, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | 3 bedrooms 2 bathrooms 2 car park for sale |  | by | Private advertiser | Apartment For Sale | listed 4 days ago | RM 340,000 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Below Market Attractive Unit |  | by | Private advertiser | Apartment For Sale | listed 4 days ago | RM 299,950 | Taman Kristal, Tanjong Tokong |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | An airy and pleasant unit on the top most floor with scenic views |  | by | Private advertiser | Condominium For Sale | listed 6 days ago | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah |  | by | Private advertiser | Apartment For Sale | listed 1 week ago | RM 530,000 | Skyridge Apartment, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Taman Skyridge Apartment |  | by | Private advertiser | Townhouse For Sale | listed 1 week ago | RM 580,000 | Tanjung Bungah, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Quiet Townhouse with Seaview |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 530,000 | I-Santorini, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Santorini renovated |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 3,300,000 | One Tanjong, Tanjung Bungah |  | 4,756 |  | sq.ft |  | 5 |  | Bed |  | 5 |  | Bath |  | Freehold |  | Luxury Apartment with Unobstructed Sea View – Best Price on the Market |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 799,000 | The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong |  | 1,047 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Tamarind, walking distance to Stonyhurst International School |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 600,000 | Twin Towers, Tanjung Bungah |  | 1,300 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Towers Condo, Tg Bungah |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 1,227,000 | City Of Dreams, Tanjong Tokong |  | 1,185 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | City of Dreams Seaview Condo 1185sf Fully Furnished |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 565,000 | Twin Towers, Tanjung Bungah |  | 1,248 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Tower Condo Tanjung Bunga |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 415,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 380,000 | Twin Towers, Tanjung Bungah |  | 926 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Furnished with nice seaview |  | by | Private advertiser | Apartment For Sale | listed 2 weeks ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Puncak Erskine 88 Full Furnished &amp; Renovated |  | by | Private advertiser | 1.5-storey Terraced House For Sale | listed 2 weeks ago | RM 899,000 | Tanjong Tokong, Penang |  | 1,900 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | 1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney |  | by | Private advertiser | Shop lot For Sale | listed 2 weeks ago | RM 689,000 | Tanjong Tokong, Penang |  | 930 |  | sq.ft |  | Freehold |  | Island 88 Shoplot (1st Floor) |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 638,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Resident Condominium |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 550,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI Pinnacle |  | by | Private advertiser | Apartment For Sale | listed 2 weeks ago | RM 240,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Puncak Erskine Apartment |  | by | Private advertiser | 1 | 2 | 3 | Explore More on Mudah | selangor | corner | puchong | ampang | kajang | klang | shah alam | corner lot | cyberjaya | cheras | toyota wish | nissan x-trail hybrid | auto selection | parkview towers | mercedes s580e | milano eight kuching | harga x adv 750 second | pangsapuri laksamana batu caves | hulu langat | pangsapuri setia impian |  | ADVERTISEMENT |  | SAVE SEARCH | Popular Locations in Malaysia | Selangor | Penang | Johor | Show More | Popular Property Type in Malaysia | Apartments | Houses | Commercial Properties | Show More | Popular Properties by Budget in Malaysia | Under RM 200 K | Under RM 300 K | Under RM 400 K | Show More | Popular Properties by Bedrooms in Malaysia | 1 Bedroom in Apartments | 2 Bedrooms in Apartments | 3 Bedrooms in Apartments | Show More |  | ADVERTISEMENT</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-07-02 05:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>117 results found: All Properties For Sale in Minden Heights, Persiaran Gurney, Pulau Tikus, Tanjong Tokong and Tanjung Bungah</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RM 15,933,500</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Tanjung Bungah</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.mudah.my/city-of-dream-condominiums-house-gurney-sea-view-115155857.htm</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Condominium For Sale | listed 2 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Apartment For Sale
+listed 22 hours ago
+RM 360,000
+Skyridge Apartment, Tanjong Tokong
+750
+sq.ft
+3
+Bed
+2
+Bath
+Freehold
+[RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>RM 360,000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.mudah.my/rare-unit-skyridge-apartment-for-sales-tanjong-tokong-gurney-115113858.htm</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>117 results found: All Properties For Sale in Minden Heights, Persiaran Gurney, Pulau Tikus, Tanjong Tokong and Tanjung Bungah | All (2,299) | By Owner (117) | By Agents (2,182) | SORT | Condominium For Sale | listed 1 hour ago | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view |  | by | Private advertiser | Condominium For Sale | listed 2 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only |  | by | Private advertiser | Condominium For Sale | listed 2 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only |  | by | Private advertiser | Apartment For Sale | listed 22 hours ago | RM 360,000 | Skyridge Apartment, Tanjong Tokong |  | 750 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | [RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney |  | by | Private advertiser | Condominium For Sale | listed 22 hours ago | RM 335,000 | Azuria, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Azuria Condominium - Direct Owner |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 600,000 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Marine Mansion |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 1,200,000 | Quayside, Tanjong Tokong |  | 1,137 |  | sq.ft |  | 1 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 368,000 | 5% | RM 388,000 | Hillside Garden, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tanjong Bungah Hillside Garden Apartment For Sale. |  | by | Private advertiser | Condominium For Sale | listed 2 days ago | RM 353,800 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tg Tokong Apartment - Fully Furnished with 2 carparks |  | by | Private advertiser | Semi-Detached House For Sale | listed 3 days ago | RM 1,650,000 | Tanjung Bungah, Penang |  | 4,395 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Single Storey Semi D House Hillside,Tanjung Bungah,Penang. |  | by | Private advertiser | Apartment For Sale | listed 3 days ago | RM 342,000 | E Garden, Tanjong Tokong |  | 760 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | E Garden apartment for sale |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 538,000 | I-Santorini, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Direct Owner Fully Furnished Nice Santorini with 3 carparks |  | by | Private advertiser | 1-storey Terraced House For Sale | listed 3 days ago | RM 410,000 | Tanjong Tokong, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold |  | by | Private advertiser | Townhouse For Sale | listed 3 days ago | RM 760,000 | Tanjung Bungah, Penang |  | 1,200 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | House for sale |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 530,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Condominium |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 500,000 | Tri Pinnacle, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong, |  | by | Private advertiser | Condominium For Sale | listed 3 days ago | RM 528,000 | The Peak Residences, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The peak RENO to TWO room |  | by | Private advertiser | Apartment For Sale | listed 3 days ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 1 |  | Bath |  | Freehold |  | Apartment For Sale |  | by | Private advertiser | Service Residence For Sale | listed 3 days ago | RM 2,500,000 | Straits Quay, Tanjong Tokong |  | 1,296 |  | sq.ft |  | 2 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Straits Residence one of the best Investment |  | by | Private advertiser | Condominium For Sale | listed 4 days ago | RM 608,000 | I-Santorini, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | 3 bedrooms 2 bathrooms 2 car park for sale |  | by | Private advertiser | Apartment For Sale | listed 4 days ago | RM 340,000 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Below Market Attractive Unit |  | by | Private advertiser | Apartment For Sale | listed 4 days ago | RM 299,950 | Taman Kristal, Tanjong Tokong |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | An airy and pleasant unit on the top most floor with scenic views |  | by | Private advertiser | Condominium For Sale | listed 6 days ago | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah |  | by | Private advertiser | Apartment For Sale | listed 1 week ago | RM 530,000 | Skyridge Apartment, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Taman Skyridge Apartment |  | by | Private advertiser | Townhouse For Sale | listed 1 week ago | RM 580,000 | Tanjung Bungah, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Quiet Townhouse with Seaview |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 530,000 | I-Santorini, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Santorini renovated |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 3,300,000 | One Tanjong, Tanjung Bungah |  | 4,756 |  | sq.ft |  | 5 |  | Bed |  | 5 |  | Bath |  | Freehold |  | Luxury Apartment with Unobstructed Sea View – Best Price on the Market |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 799,000 | The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong |  | 1,047 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Tamarind, walking distance to Stonyhurst International School |  | by | Private advertiser | Condominium For Sale | listed 1 week ago | RM 600,000 | Twin Towers, Tanjung Bungah |  | 1,300 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Towers Condo, Tg Bungah |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 1,227,000 | City Of Dreams, Tanjong Tokong |  | 1,185 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | City of Dreams Seaview Condo 1185sf Fully Furnished |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 565,000 | Twin Towers, Tanjung Bungah |  | 1,248 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Tower Condo Tanjung Bunga |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 415,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 380,000 | Twin Towers, Tanjung Bungah |  | 926 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Furnished with nice seaview |  | by | Private advertiser | Apartment For Sale | listed 2 weeks ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Puncak Erskine 88 Full Furnished &amp; Renovated |  | by | Private advertiser | 1.5-storey Terraced House For Sale | listed 2 weeks ago | RM 899,000 | Tanjong Tokong, Penang |  | 1,900 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | 1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney |  | by | Private advertiser | Shop lot For Sale | listed 2 weeks ago | RM 689,000 | Tanjong Tokong, Penang |  | 930 |  | sq.ft |  | Freehold |  | Island 88 Shoplot (1st Floor) |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 638,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Resident Condominium |  | by | Private advertiser | Condominium For Sale | listed 2 weeks ago | RM 550,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI Pinnacle |  | by | Private advertiser | Apartment For Sale | listed 2 weeks ago | RM 240,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Puncak Erskine Apartment |  | by | Private advertiser | 1 | 2 | 3 | Explore More on Mudah | selangor | corner | puchong | ampang | kajang | klang | shah alam | corner lot | cyberjaya | cheras | toyota wish | nissan x-trail hybrid | auto selection | parkview towers | mercedes s580e | milano eight kuching | harga x adv 750 second | pangsapuri laksamana batu caves | hulu langat | pangsapuri setia impian |  | ADVERTISEMENT |  | SAVE SEARCH | Popular Locations in Malaysia | Selangor | Penang | Johor | Show More | Popular Property Type in Malaysia | Apartments | Houses | Commercial Properties | Show More | Popular Properties by Budget in Malaysia | Under RM 200 K | Under RM 300 K | Under RM 400 K | Show More | Popular Properties by Bedrooms in Malaysia | 1 Bedroom in Apartments | 2 Bedrooms in Apartments | 3 Bedrooms in Apartments | Show More |  | ADVERTISEMENT</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-07-02 05:24</t>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Apartment For Sale | listed 22 hours ago | RM 360,000 | Skyridge Apartment, Tanjong Tokong |  | 750 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | [RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-07-02 05:29</t>
         </is>
       </c>
     </row>

--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Penang Listings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,22 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -491,6 +477,21 @@
           <t>Scraped At</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Seller Name</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Contact Fetch Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -513,20 +514,14 @@
           <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>800</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -548,49 +543,54 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Joined since: Mar 2018</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Puncak Erskine Apartment</t>
+          <t>The Peak Resident Condominium</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RM 240,000</t>
+          <t>RM 638,000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Puncak Erskine, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+          <t>The Peak Residences, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1100</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/puncak-erskine-apartment-114957457.htm</t>
+          <t>https://www.mudah.my/the-peak-resident-condominium-114960623.htm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -603,54 +603,55 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 2 weeks ago | RM 240,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Puncak Erskine Apartment</t>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 638,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Resident Condominium</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Joined since: Jun 2026</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The Peak Resident Condominium</t>
+          <t>Island 88 Shoplot (1st Floor)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Shop lot</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RM 638,000</t>
+          <t>RM 689,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The Peak Residences, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
+          <t>Tanjong Tokong, Penang</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>930</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-peak-resident-condominium-114960623.htm</t>
+          <t>https://www.mudah.my/island-88-shoplot-1st-floor-114982296.htm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -663,29 +664,40 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 weeks ago | RM 638,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Resident Condominium</t>
+          <t>Shop lot For Sale | listed 2 weeks ago | RM 689,000 | Tanjong Tokong, Penang |  | 930 |  | sq.ft |  | Freehold |  | Island 88 Shoplot (1st Floor)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Joined since: Mar 2021</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Island 88 Shoplot (1st Floor)</t>
+          <t>1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shop lot</t>
+          <t>1.5-storey Terraced House</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RM 689,000</t>
+          <t>RM 899,000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -693,16 +705,18 @@
           <t>Tanjong Tokong, Penang</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1900</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/island-88-shoplot-1st-floor-114982296.htm</t>
+          <t>https://www.mudah.my/1-5-storey-terraced-house-tanjung-tokong-near-straight-quay-gurney-114981119.htm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -715,54 +729,59 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Shop lot For Sale | listed 2 weeks ago | RM 689,000 | Tanjong Tokong, Penang |  | 930 |  | sq.ft |  | Freehold |  | Island 88 Shoplot (1st Floor)</t>
+          <t>1.5-storey Terraced House For Sale | listed 2 weeks ago | RM 899,000 | Tanjong Tokong, Penang |  | 1,900 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | 1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Joined since: Mar 2021</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
+          <t>Puncak Erskine 88 Full Furnished &amp; Renovated</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.5-storey Terraced House</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RM 899,000</t>
+          <t>RM 180,000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tanjong Tokong, Penang</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1900</t>
-        </is>
+          <t>Puncak Erskine, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>650</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/1-5-storey-terraced-house-tanjung-tokong-near-straight-quay-gurney-114981119.htm</t>
+          <t>https://www.mudah.my/puncak-erskine-88-full-furnished-renovated-115022482.htm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -775,54 +794,59 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.5-storey Terraced House For Sale | listed 2 weeks ago | RM 899,000 | Tanjong Tokong, Penang |  | 1,900 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | 1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
+          <t>Apartment For Sale | listed 2 weeks ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Puncak Erskine 88 Full Furnished &amp; Renovated</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Joined since: Jun 2026</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Puncak Erskine 88 Full Furnished &amp; Renovated</t>
+          <t>Furnished with nice seaview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RM 180,000</t>
+          <t>RM 380,000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Puncak Erskine, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+          <t>Twin Towers, Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>926</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/puncak-erskine-88-full-furnished-renovated-115022482.htm</t>
+          <t>https://www.mudah.my/furnished-with-nice-seaview-114995729.htm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -835,19 +859,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 2 weeks ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Puncak Erskine 88 Full Furnished &amp; Renovated</t>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 380,000 | Twin Towers, Tanjung Bungah |  | 926 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Furnished with nice seaview</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Furnished with nice seaview</t>
+          <t>Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -857,32 +884,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RM 380,000</t>
+          <t>RM 415,000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Twin Towers, Tanjung Bungah</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>800</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/furnished-with-nice-seaview-114995729.htm</t>
+          <t>https://www.mudah.my/tri-pinnacle-condo-tanjong-tokong-800sf-for-sale-original-unit-114993450.htm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -895,19 +916,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 weeks ago | RM 380,000 | Twin Towers, Tanjung Bungah |  | 926 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Furnished with nice seaview</t>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 415,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
+          <t>Twin Tower Condo Tanjung Bunga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -917,32 +941,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RM 415,000</t>
+          <t>RM 565,000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+          <t>Twin Towers, Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1248</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-condo-tanjong-tokong-800sf-for-sale-original-unit-114993450.htm</t>
+          <t>https://www.mudah.my/twin-tower-condo-tanjung-bunga-114995728.htm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -955,19 +973,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 weeks ago | RM 415,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 565,000 | Twin Towers, Tanjung Bungah |  | 1,248 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Tower Condo Tanjung Bunga</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Twin Tower Condo Tanjung Bunga</t>
+          <t>City of Dreams Seaview Condo 1185sf Fully Furnished</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -977,32 +998,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RM 565,000</t>
+          <t>RM 1,227,000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Twin Towers, Tanjung Bungah</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
+          <t>City Of Dreams, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1185</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/twin-tower-condo-tanjung-bunga-114995728.htm</t>
+          <t>https://www.mudah.my/city-of-dreams-seaview-condo-1185sf-fully-furnished-115000031.htm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1015,19 +1030,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 weeks ago | RM 565,000 | Twin Towers, Tanjung Bungah |  | 1,248 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Tower Condo Tanjung Bunga</t>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 1,227,000 | City Of Dreams, Tanjong Tokong |  | 1,185 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | City of Dreams Seaview Condo 1185sf Fully Furnished</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>City of Dreams Seaview Condo 1185sf Fully Furnished</t>
+          <t>tri pinnacle tanjung tokong</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1037,62 +1055,59 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RM 1,227,000</t>
+          <t>RM 450,000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>City Of Dreams, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1185</t>
-        </is>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>800</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/city-of-dreams-seaview-condo-1185sf-fully-furnished-115000031.htm</t>
+          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-115045263.htm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 weeks ago | RM 1,227,000 | City Of Dreams, Tanjong Tokong |  | 1,185 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | City of Dreams Seaview Condo 1185sf Fully Furnished</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Taman Skyridge Apartment</t>
+          <t>Santorini renovated</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1102,27 +1117,21 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Skyridge Apartment, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
+          <t>I-Santorini, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/taman-skyridge-apartment-115060516.htm</t>
+          <t>https://www.mudah.my/santorini-renovated-115045187.htm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1135,54 +1144,51 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 1 week ago | RM 530,000 | Skyridge Apartment, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Taman Skyridge Apartment</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 530,000 | I-Santorini, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Santorini renovated</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tri pinnacle tanjung tokong</t>
+          <t>Taman Skyridge Apartment</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RM 450,000</t>
+          <t>RM 530,000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+          <t>Skyridge Apartment, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>850</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-115045263.htm</t>
+          <t>https://www.mudah.my/taman-skyridge-apartment-115060516.htm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1195,19 +1201,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong</t>
+          <t>Apartment For Sale | listed 1 week ago | RM 530,000 | Skyridge Apartment, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Taman Skyridge Apartment</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Twin Towers Condo, Tg Bungah</t>
+          <t>The Tamarind, walking distance to Stonyhurst International School</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1217,32 +1226,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RM 600,000</t>
+          <t>RM 799,000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Twin Towers, Tanjung Bungah</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
+          <t>The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1047</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/twin-towers-condo-tg-bungah-115027655.htm</t>
+          <t>https://www.mudah.my/the-tamarind-walking-distance-to-stonyhurst-international-school-115026766.htm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1255,19 +1258,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 600,000 | Twin Towers, Tanjung Bungah |  | 1,300 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Towers Condo, Tg Bungah</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 799,000 | The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong |  | 1,047 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Tamarind, walking distance to Stonyhurst International School</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>The Tamarind, walking distance to Stonyhurst International School</t>
+          <t>Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1277,32 +1283,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RM 799,000</t>
+          <t>RM 3,300,000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
+          <t>One Tanjong, Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4756</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-tamarind-walking-distance-to-stonyhurst-international-school-115026766.htm</t>
+          <t>https://www.mudah.my/luxury-apartment-with-unobstructed-sea-view-best-price-on-the-market-115022080.htm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1315,54 +1315,51 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 799,000 | The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong |  | 1,047 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Tamarind, walking distance to Stonyhurst International School</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 3,300,000 | One Tanjong, Tanjung Bungah |  | 4,756 |  | sq.ft |  | 5 |  | Bed |  | 5 |  | Bath |  | Freehold |  | Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Quiet Townhouse with Seaview</t>
+          <t>Twin Towers Condo, Tg Bungah</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RM 580,000</t>
+          <t>RM 600,000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tanjung Bungah, Penang</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+          <t>Twin Towers, Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1300</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/quiet-townhouse-with-seaview-115045058.htm</t>
+          <t>https://www.mudah.my/twin-towers-condo-tg-bungah-115027655.htm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1375,54 +1372,51 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Townhouse For Sale | listed 1 week ago | RM 580,000 | Tanjung Bungah, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Quiet Townhouse with Seaview</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 600,000 | Twin Towers, Tanjung Bungah |  | 1,300 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Towers Condo, Tg Bungah</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Santorini renovated</t>
+          <t>Quiet Townhouse with Seaview</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RM 530,000</t>
+          <t>RM 580,000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>I-Santorini, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+          <t>Tanjung Bungah, Penang</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1000</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/santorini-renovated-115045187.htm</t>
+          <t>https://www.mudah.my/quiet-townhouse-with-seaview-115045058.htm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1435,19 +1429,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 530,000 | I-Santorini, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Santorini renovated</t>
+          <t>Townhouse For Sale | listed 1 week ago | RM 580,000 | Tanjung Bungah, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Quiet Townhouse with Seaview</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
+          <t>Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1457,57 +1454,54 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RM 3,300,000</t>
+          <t>RM 4,800,000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>One Tanjong, Tanjung Bungah</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>4756</t>
-        </is>
+          <t>Springtide Residences, Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5221</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/luxury-apartment-with-unobstructed-sea-view-best-price-on-the-market-115022080.htm</t>
+          <t>https://www.mudah.my/springtide-residences-beachfront-luxury-condominium-in-tanjung-bungah-115100943.htm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 3,300,000 | One Tanjong, Tanjung Bungah |  | 4,756 |  | sq.ft |  | 5 |  | Bed |  | 5 |  | Bath |  | Freehold |  | Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
+          <t>Condominium For Sale | listed 6 days ago | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
+          <t>3 bedrooms 2 bathrooms 2 car park for sale</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1517,112 +1511,106 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RM 4,800,000</t>
+          <t>RM 608,000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Springtide Residences, Tanjung Bungah</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>5221</t>
-        </is>
+          <t>I-Santorini, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>800</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/springtide-residences-beachfront-luxury-condominium-in-tanjung-bungah-115100943.htm</t>
+          <t>https://www.mudah.my/3-bedrooms-2-bathrooms-2-car-park-for-sale-115083940.htm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 6 days ago | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
+          <t>Condominium For Sale | listed 5 days ago | RM 608,000 | I-Santorini, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | 3 bedrooms 2 bathrooms 2 car park for sale</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3 bedrooms 2 bathrooms 2 car park for sale</t>
+          <t>Below Market Attractive Unit</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RM 608,000</t>
+          <t>RM 340,000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>I-Santorini, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>650</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/3-bedrooms-2-bathrooms-2-car-park-for-sale-115083940.htm</t>
+          <t>https://www.mudah.my/below-market-attractive-unit-115034831.htm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 4 days ago | RM 608,000 | I-Santorini, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | 3 bedrooms 2 bathrooms 2 car park for sale</t>
+          <t>Apartment For Sale | listed 5 days ago | RM 340,000 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Below Market Attractive Unit</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1645,20 +1633,14 @@
           <t>Taman Kristal, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>700</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1667,62 +1649,59 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 4 days ago | RM 299,950 | Taman Kristal, Tanjong Tokong |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | An airy and pleasant unit on the top most floor with scenic views</t>
+          <t>Apartment For Sale | listed 5 days ago | RM 299,950 | Taman Kristal, Tanjong Tokong |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | An airy and pleasant unit on the top most floor with scenic views</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Below Market Attractive Unit</t>
+          <t>Straits Residence one of the best Investment</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Service Residence</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RM 340,000</t>
+          <t>RM 2,500,000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+          <t>Straits Quay, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1296</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/below-market-attractive-unit-115034831.htm</t>
+          <t>https://www.mudah.my/straits-residence-one-of-the-best-investment-115089396.htm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1735,19 +1714,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 4 days ago | RM 340,000 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Below Market Attractive Unit</t>
+          <t>Service Residence For Sale | listed 4 days ago | RM 2,500,000 | Straits Quay, Tanjong Tokong |  | 1,296 |  | sq.ft |  | 2 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Straits Residence one of the best Investment</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E Garden apartment for sale</t>
+          <t>Apartment For Sale</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1757,177 +1739,168 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RM 342,000</t>
+          <t>RM 180,000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>E Garden, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
+          <t>Puncak Erskine, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>600</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/e-garden-apartment-for-sale-115127752.htm</t>
+          <t>https://www.mudah.my/apartment-for-sale-115093031.htm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 3 days ago | RM 342,000 | E Garden, Tanjong Tokong |  | 760 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | E Garden apartment for sale</t>
+          <t>Apartment For Sale | listed 4 days ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 1 |  | Bath |  | Freehold |  | Apartment For Sale</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Straits Residence one of the best Investment</t>
+          <t>The peak RENO to TWO room</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Service Residence</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RM 2,500,000</t>
+          <t>RM 528,000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Straits Quay, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
+          <t>The Peak Residences, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/straits-residence-one-of-the-best-investment-115089396.htm</t>
+          <t>https://www.mudah.my/the-peak-reno-to-two-room-115092789.htm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Service Residence For Sale | listed 3 days ago | RM 2,500,000 | Straits Quay, Tanjong Tokong |  | 1,296 |  | sq.ft |  | 2 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Straits Residence one of the best Investment</t>
+          <t>Condominium For Sale | listed 4 days ago | RM 528,000 | The Peak Residences, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The peak RENO to TWO room</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Apartment For Sale</t>
+          <t>The Peak Condominium</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RM 180,000</t>
+          <t>RM 530,000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Puncak Erskine, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
+          <t>The Peak Residences, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1100</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/apartment-for-sale-115093031.htm</t>
+          <t>https://www.mudah.my/the-peak-condominium-115093455.htm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 3 days ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 1 |  | Bath |  | Freehold |  | Apartment For Sale</t>
+          <t>Condominium For Sale | listed 4 days ago | RM 530,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Condominium</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>The Peak Condominium</t>
+          <t>TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1937,92 +1910,83 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RM 530,000</t>
+          <t>RM 500,000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>The Peak Residences, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>850</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-peak-condominium-115093455.htm</t>
+          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-jalan-persiaran-halia-3-tanjung-tokong-115090201.htm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 3 days ago | RM 530,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Condominium</t>
+          <t>Condominium For Sale | listed 4 days ago | RM 500,000 | Tri Pinnacle, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
+          <t>E Garden apartment for sale</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RM 538,000</t>
+          <t>RM 342,000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>I-Santorini, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
+          <t>E Garden, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>760</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/direct-owner-fully-furnished-nice-santorini-with-3-carparks-115127587.htm</t>
+          <t>https://www.mudah.my/e-garden-apartment-for-sale-115127752.htm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2035,14 +1999,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 3 days ago | RM 538,000 | I-Santorini, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
+          <t>Apartment For Sale | listed 3 days ago | RM 342,000 | E Garden, Tanjong Tokong |  | 760 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | E Garden apartment for sale</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2065,20 +2032,14 @@
           <t>Tanjung Bungah, Penang</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>4395</t>
-        </is>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4395</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2100,14 +2061,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>The peak RENO to TWO room</t>
+          <t>Tanjong Bungah Hillside Garden Apartment For Sale.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2117,32 +2081,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RM 528,000</t>
+          <t>RM 368,000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The Peak Residences, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+          <t>Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>700</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-peak-reno-to-two-room-115092789.htm</t>
+          <t>https://www.mudah.my/tanjong-bungah-hillside-garden-apartment-for-sale-114853211.htm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2155,54 +2113,51 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 3 days ago | RM 528,000 | The Peak Residences, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The peak RENO to TWO room</t>
+          <t>Condominium For Sale | listed 3 days ago | RM 368,000 | 5% | RM 388,000 | Hillside Garden, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tanjong Bungah Hillside Garden Apartment For Sale.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
+          <t>TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>1-storey Terraced House</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RM 500,000</t>
+          <t>RM 410,000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
+          <t>Tanjong Tokong, Penang</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1000</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-jalan-persiaran-halia-3-tanjung-tokong-115090201.htm</t>
+          <t>https://www.mudah.my/taman-intan-delima-single-storey-terrace-batu-kawan-freehold-115126865.htm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2215,54 +2170,51 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 3 days ago | RM 500,000 | Tri Pinnacle, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
+          <t>1-storey Terraced House For Sale | listed 3 days ago | RM 410,000 | Tanjong Tokong, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>House for sale</t>
+          <t>Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RM 760,000</t>
+          <t>RM 538,000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tanjung Bungah, Penang</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
+          <t>I-Santorini, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>850</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/house-for-sale-108064933.htm</t>
+          <t>https://www.mudah.my/direct-owner-fully-furnished-nice-santorini-with-3-carparks-115127587.htm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2275,54 +2227,51 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Townhouse For Sale | listed 3 days ago | RM 760,000 | Tanjung Bungah, Penang |  | 1,200 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | House for sale</t>
+          <t>Condominium For Sale | listed 3 days ago | RM 538,000 | I-Santorini, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
+          <t>House for sale</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1-storey Terraced House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RM 410,000</t>
+          <t>RM 760,000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tanjong Tokong, Penang</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+          <t>Tanjung Bungah, Penang</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1200</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/taman-intan-delima-single-storey-terrace-batu-kawan-freehold-115126865.htm</t>
+          <t>https://www.mudah.my/house-for-sale-108064933.htm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2335,19 +2284,22 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1-storey Terraced House For Sale | listed 3 days ago | RM 410,000 | Tanjong Tokong, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
+          <t>Townhouse For Sale | listed 3 days ago | RM 760,000 | Tanjung Bungah, Penang |  | 1,200 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | House for sale</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
+          <t>Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2357,57 +2309,54 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RM 1,200,000</t>
+          <t>RM 353,800</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Quayside, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1137</t>
-        </is>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>650</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/pinang-quayside-condo-fully-furnished-1bedroom-2-bathrooms-unit-103758517.htm</t>
+          <t>https://www.mudah.my/tg-tokong-apartment-fully-furnished-with-2-carparks-115129412.htm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 days ago | RM 1,200,000 | Quayside, Tanjong Tokong |  | 1,137 |  | sq.ft |  | 1 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
+          <t>Condominium For Sale | listed 3 days ago | RM 353,800 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tanjong Bungah Hillside Garden Apartment For Sale.</t>
+          <t>Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2417,32 +2366,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RM 368,000</t>
+          <t>RM 1,200,000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tanjung Bungah</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
+          <t>Quayside, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1137</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tanjong-bungah-hillside-garden-apartment-for-sale-114853211.htm</t>
+          <t>https://www.mudah.my/pinang-quayside-condo-fully-furnished-1bedroom-2-bathrooms-unit-103758517.htm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2455,14 +2398,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 days ago | RM 368,000 | 5% | RM 388,000 | Hillside Garden, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tanjong Bungah Hillside Garden Apartment For Sale.</t>
+          <t>Condominium For Sale | listed 2 days ago | RM 1,200,000 | Quayside, Tanjong Tokong |  | 1,137 |  | sq.ft |  | 1 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2485,20 +2431,14 @@
           <t>Marine Mansion, Tanjung Bungah</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>850</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2520,14 +2460,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
+          <t>Azuria Condominium - Direct Owner</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2537,92 +2480,83 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RM 353,800</t>
+          <t>RM 335,000</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+          <t>Azuria, Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>700</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tg-tokong-apartment-fully-furnished-with-2-carparks-115129412.htm</t>
+          <t>https://www.mudah.my/azuria-condominium-direct-owner-111620926.htm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 days ago | RM 353,800 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
+          <t>Condominium For Sale | listed 1 day ago | RM 335,000 | Azuria, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Azuria Condominium - Direct Owner</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azuria Condominium - Direct Owner</t>
+          <t>[RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RM 335,000</t>
+          <t>RM 360,000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Azuria, Tanjung Bungah</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
+          <t>Skyridge Apartment, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>750</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/azuria-condominium-direct-owner-111620926.htm</t>
+          <t>https://www.mudah.my/rare-unit-skyridge-apartment-for-sales-tanjong-tokong-gurney-115113858.htm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2631,23 +2565,26 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 23 hours ago | RM 335,000 | Azuria, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Azuria Condominium - Direct Owner</t>
+          <t>Apartment For Sale | listed 1 day ago | RM 360,000 | Skyridge Apartment, Tanjong Tokong |  | 750 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | [RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>city of dream condominiums house gurney sea view</t>
+          <t>Andaman</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2657,32 +2594,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RM 15,933,500</t>
+          <t>RM 4,000,000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>City Of Dreams, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
+          <t>18 East @ Andaman, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2827</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/city-of-dream-condominiums-house-gurney-sea-view-115155857.htm</t>
+          <t>https://www.mudah.my/andaman-115157424.htm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2695,19 +2626,22 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 hour ago | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view</t>
+          <t>Condominium For Sale | listed 1 hour ago | RM 4,000,000 | 18 East @ Andaman, Tanjong Tokong |  | 2,827 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Andaman</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Looking For Investors Only</t>
+          <t>city of dream condominiums house gurney sea view</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2717,32 +2651,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RM 598,888</t>
+          <t>RM 15,933,500</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Marine Mansion, Tanjung Bungah</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
+          <t>City Of Dreams, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1500</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/looking-for-investors-only-115155444.htm</t>
+          <t>https://www.mudah.my/city-of-dream-condominiums-house-gurney-sea-view-115155857.htm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2755,14 +2683,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+          <t>Condominium For Sale | listed 3 hours ago | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2777,32 +2708,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RM 888,888</t>
+          <t>RM 598,888</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Desa Mas (Pulau Tikus), Pulau Tikus</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1089</t>
-        </is>
+          <t>Marine Mansion, Tanjung Bungah</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>850</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/looking-for-investors-only-115155435.htm</t>
+          <t>https://www.mudah.my/looking-for-investors-only-115155444.htm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2815,59 +2740,56 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+          <t>Condominium For Sale | listed 3 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
+          <t>Looking For Investors Only</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RM 360,000</t>
+          <t>RM 888,888</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Skyridge Apartment, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
+          <t>Desa Mas (Pulau Tikus), Pulau Tikus</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1089</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/rare-unit-skyridge-apartment-for-sales-tanjong-tokong-gurney-115113858.htm</t>
+          <t>https://www.mudah.my/looking-for-investors-only-115155435.htm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -2875,14 +2797,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 22 hours ago | RM 360,000 | Skyridge Apartment, Tanjong Tokong |  | 750 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | [RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
+          <t>Condominium For Sale | listed 3 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-02 05:32</t>
-        </is>
-      </c>
+          <t>2026-07-02 07:08</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Penang Listings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,8 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -477,21 +491,6 @@
           <t>Scraped At</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Seller Name</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Contact Fetch Status</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -514,14 +513,20 @@
           <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>800</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -543,18 +548,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Joined since: Mar 2018</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>2026-07-02 07:11</t>
         </is>
       </c>
     </row>
@@ -579,14 +573,20 @@
           <t>The Peak Residences, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1100</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -608,18 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Joined since: Jun 2026</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>2026-07-02 07:11</t>
         </is>
       </c>
     </row>
@@ -646,8 +635,10 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>930</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -669,18 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Joined since: Mar 2021</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>2026-07-02 07:11</t>
         </is>
       </c>
     </row>
@@ -705,14 +685,20 @@
           <t>Tanjong Tokong, Penang</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1900</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -734,18 +720,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Joined since: Mar 2021</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>2026-07-02 07:11</t>
         </is>
       </c>
     </row>
@@ -770,14 +745,20 @@
           <t>Puncak Erskine, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>650</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -799,18 +780,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Joined since: Jun 2026</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>2026-07-02 07:11</t>
         </is>
       </c>
     </row>
@@ -835,14 +805,20 @@
           <t>Twin Towers, Tanjung Bungah</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>926</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -864,12 +840,9 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -892,14 +865,20 @@
           <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>800</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -921,12 +900,9 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -949,14 +925,20 @@
           <t>Twin Towers, Tanjung Bungah</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1248</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -978,12 +960,9 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1006,14 +985,20 @@
           <t>City Of Dreams, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1185</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1185</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1035,12 +1020,9 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1063,14 +1045,20 @@
           <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>800</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1092,12 +1080,9 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1120,14 +1105,20 @@
           <t>I-Santorini, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1000</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1149,12 +1140,9 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1177,14 +1165,20 @@
           <t>Skyridge Apartment, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>850</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1206,12 +1200,9 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1234,14 +1225,20 @@
           <t>The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1047</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1263,12 +1260,9 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1291,14 +1285,20 @@
           <t>One Tanjong, Tanjung Bungah</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4756</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4756</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1320,12 +1320,9 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1348,14 +1345,20 @@
           <t>Twin Towers, Tanjung Bungah</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1300</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1377,12 +1380,9 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1405,14 +1405,20 @@
           <t>Tanjung Bungah, Penang</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1000</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1434,12 +1440,9 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1462,14 +1465,20 @@
           <t>Springtide Residences, Tanjung Bungah</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5221</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5221</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1491,12 +1500,9 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1519,14 +1525,20 @@
           <t>I-Santorini, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" t="n">
-        <v>800</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1548,12 +1560,9 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1576,14 +1585,20 @@
           <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="n">
-        <v>650</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1605,12 +1620,9 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1633,14 +1645,20 @@
           <t>Taman Kristal, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>700</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1662,12 +1680,9 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1690,14 +1705,20 @@
           <t>Straits Quay, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1296</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1719,12 +1740,9 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1747,14 +1765,20 @@
           <t>Puncak Erskine, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>600</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1776,12 +1800,9 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1804,14 +1825,20 @@
           <t>The Peak Residences, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1000</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1833,12 +1860,9 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1861,14 +1885,20 @@
           <t>The Peak Residences, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1100</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1890,12 +1920,9 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1918,14 +1945,20 @@
           <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>850</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1947,12 +1980,9 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1975,14 +2005,20 @@
           <t>E Garden, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" t="n">
-        <v>760</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2004,12 +2040,9 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2032,14 +2065,20 @@
           <t>Tanjung Bungah, Penang</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4395</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>4395</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2061,12 +2100,9 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2089,14 +2125,20 @@
           <t>Tanjung Bungah</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" t="n">
-        <v>700</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2118,12 +2160,9 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2146,14 +2185,20 @@
           <t>Tanjong Tokong, Penang</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>3</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1000</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2175,12 +2220,9 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2203,14 +2245,20 @@
           <t>I-Santorini, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" t="n">
-        <v>850</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2232,12 +2280,9 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2260,14 +2305,20 @@
           <t>Tanjung Bungah, Penang</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1200</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2289,12 +2340,9 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2317,14 +2365,20 @@
           <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" t="n">
-        <v>650</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2346,12 +2400,9 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2374,14 +2425,20 @@
           <t>Quayside, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1137</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1137</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2403,12 +2460,9 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2431,14 +2485,20 @@
           <t>Marine Mansion, Tanjung Bungah</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>3</v>
-      </c>
-      <c r="F35" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" t="n">
-        <v>850</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2460,12 +2520,9 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2488,14 +2545,20 @@
           <t>Azuria, Tanjung Bungah</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" t="n">
-        <v>700</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2517,12 +2580,9 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2545,14 +2605,20 @@
           <t>Skyridge Apartment, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>3</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="n">
-        <v>750</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2574,12 +2640,9 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2602,14 +2665,20 @@
           <t>18 East @ Andaman, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>3</v>
-      </c>
-      <c r="F38" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2827</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2827</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2631,12 +2700,9 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2659,14 +2725,20 @@
           <t>City Of Dreams, Tanjong Tokong</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>4</v>
-      </c>
-      <c r="F39" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1500</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2688,12 +2760,9 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2716,14 +2785,20 @@
           <t>Marine Mansion, Tanjung Bungah</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" t="n">
-        <v>850</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2740,17 +2815,14 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 3 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+          <t>Condominium For Sale | listed 4 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2773,14 +2845,20 @@
           <t>Desa Mas (Pulau Tikus), Pulau Tikus</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>5</v>
-      </c>
-      <c r="F41" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1089</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2797,17 +2875,14 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 3 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+          <t>Condominium For Sale | listed 4 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-02 07:08</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+          <t>2026-07-02 07:11</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-02 07:11</t>
+          <t>2026-07-02 07:14</t>
         </is>
       </c>
     </row>

--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-02 07:14</t>
+          <t>2026-07-02 07:19</t>
         </is>
       </c>
     </row>

--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1020,14 +1020,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tri pinnacle tanjung tokong</t>
+          <t>Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1037,32 +1037,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RM 450,000</t>
+          <t>RM 4,800,000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>Springtide Residences, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-115045263.htm</t>
+          <t>https://www.mudah.my/springtide-residences-beachfront-luxury-condominium-in-tanjung-bungah-115100943.htm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1440,14 +1440,14 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
+          <t>tri pinnacle tanjung tokong</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1457,50 +1457,50 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RM 4,800,000</t>
+          <t>RM 450,000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Springtide Residences, Tanjung Bungah</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/springtide-residences-beachfront-luxury-condominium-in-tanjung-bungah-115100943.htm</t>
+          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-115045263.htm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 6 days ago | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-02 07:19</t>
+          <t>2026-07-02 07:23</t>
         </is>
       </c>
     </row>

--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-02 07:23</t>
+          <t>2026-07-02 07:28</t>
         </is>
       </c>
     </row>

--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 hour ago | RM 4,000,000 | 18 East @ Andaman, Tanjong Tokong |  | 2,827 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Andaman</t>
+          <t>Condominium For Sale | listed 2 hours ago | RM 4,000,000 | 18 East @ Andaman, Tanjong Tokong |  | 2,827 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Andaman</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2755,12 +2755,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 3 hours ago | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view</t>
+          <t>Condominium For Sale | listed 4 hours ago | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 4 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+          <t>Condominium For Sale | listed 5 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>
@@ -2875,12 +2875,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 4 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+          <t>Condominium For Sale | listed 5 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-02 07:28</t>
+          <t>2026-07-02 08:21</t>
         </is>
       </c>
     </row>

--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-02 08:21</t>
+          <t>2026-07-02 08:26</t>
         </is>
       </c>
     </row>

--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-02 08:26</t>
+          <t>2026-07-02 08:30</t>
         </is>
       </c>
     </row>

--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -495,7 +495,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TRI Pinnacle</t>
+          <t>Andaman</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RM 550,000</t>
+          <t>RM 4,000,000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>18 East @ Andaman, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,42 +520,36 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-114681845.htm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>14</v>
-      </c>
+          <t>https://www.mudah.my/andaman-115157424.htm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 weeks ago | RM 550,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI Pinnacle</t>
+          <t>Condominium For Sale | 2h | RM 4,000,000 | 18 East @ Andaman, Tanjong Tokong |  | 2,827 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Andaman</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>The Peak Resident Condominium</t>
+          <t>city of dream condominiums house gurney sea view</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -565,17 +559,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RM 638,000</t>
+          <t>RM 15,933,500</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The Peak Residences, Tanjong Tokong</t>
+          <t>City Of Dreams, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -585,149 +579,139 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-peak-resident-condominium-114960623.htm</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>14</v>
-      </c>
+          <t>https://www.mudah.my/city-of-dream-condominiums-house-gurney-sea-view-115155857.htm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 weeks ago | RM 638,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Resident Condominium</t>
+          <t>Condominium For Sale | 4h | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Island 88 Shoplot (1st Floor)</t>
+          <t>An airy and pleasant unit on the top most floor with scenic views</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shop lot</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RM 689,000</t>
+          <t>RM 299,950</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tanjong Tokong, Penang</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>Taman Kristal, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/island-88-shoplot-1st-floor-114982296.htm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>14</v>
-      </c>
+          <t>https://www.mudah.my/an-airy-and-pleasant-unit-on-the-top-most-floor-with-scenic-views-114303816.htm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Shop lot For Sale | listed 2 weeks ago | RM 689,000 | Tanjong Tokong, Penang |  | 930 |  | sq.ft |  | Freehold |  | Island 88 Shoplot (1st Floor)</t>
+          <t>Apartment For Sale | 5d | RM 299,950 | Taman Kristal, Tanjong Tokong |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | An airy and pleasant unit on the top most floor with scenic views</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
+          <t>Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.5-storey Terraced House</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RM 899,000</t>
+          <t>RM 4,800,000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tanjong Tokong, Penang</t>
+          <t>Springtide Residences, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/1-5-storey-terraced-house-tanjung-tokong-near-straight-quay-gurney-114981119.htm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>14</v>
-      </c>
+          <t>https://www.mudah.my/springtide-residences-beachfront-luxury-condominium-in-tanjung-bungah-115100943.htm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.5-storey Terraced House For Sale | listed 2 weeks ago | RM 899,000 | Tanjong Tokong, Penang |  | 1,900 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | 1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
+          <t>Condominium For Sale | 1w | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Puncak Erskine 88 Full Furnished &amp; Renovated</t>
+          <t>Taman Skyridge Apartment</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -737,12 +721,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RM 180,000</t>
+          <t>RM 530,000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Puncak Erskine, Tanjong Tokong</t>
+          <t>Skyridge Apartment, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -752,62 +736,56 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>850</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/puncak-erskine-88-full-furnished-renovated-115022482.htm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
+          <t>https://www.mudah.my/taman-skyridge-apartment-115060516.htm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 2 weeks ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Puncak Erskine 88 Full Furnished &amp; Renovated</t>
+          <t>Apartment For Sale | 1w | RM 530,000 | Skyridge Apartment, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Taman Skyridge Apartment</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Furnished with nice seaview</t>
+          <t>Quiet Townhouse with Seaview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RM 380,000</t>
+          <t>RM 580,000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Twin Towers, Tanjung Bungah</t>
+          <t>Tanjung Bungah, Penang</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -817,37 +795,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/furnished-with-nice-seaview-114995729.htm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>14</v>
-      </c>
+          <t>https://www.mudah.my/quiet-townhouse-with-seaview-115045058.htm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 weeks ago | RM 380,000 | Twin Towers, Tanjung Bungah |  | 926 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Furnished with nice seaview</t>
+          <t>Townhouse For Sale | 1w | RM 580,000 | Tanjung Bungah, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Quiet Townhouse with Seaview</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
+          <t>Santorini renovated</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -857,12 +829,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RM 415,000</t>
+          <t>RM 530,000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>I-Santorini, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -877,37 +849,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-condo-tanjong-tokong-800sf-for-sale-original-unit-114993450.htm</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>14</v>
-      </c>
+          <t>https://www.mudah.my/santorini-renovated-115045187.htm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 weeks ago | RM 415,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
+          <t>Condominium For Sale | 1w | RM 530,000 | I-Santorini, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Santorini renovated</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Twin Tower Condo Tanjung Bunga</t>
+          <t>tri pinnacle tanjung tokong</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -917,12 +883,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RM 565,000</t>
+          <t>RM 450,000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Twin Towers, Tanjung Bungah</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -937,37 +903,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/twin-tower-condo-tanjung-bunga-114995728.htm</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>14</v>
-      </c>
+          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-115045263.htm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 weeks ago | RM 565,000 | Twin Towers, Tanjung Bungah |  | 1,248 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Tower Condo Tanjung Bunga</t>
+          <t>Condominium For Sale | 1w | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>City of Dreams Seaview Condo 1185sf Fully Furnished</t>
+          <t>Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -977,57 +937,51 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RM 1,227,000</t>
+          <t>RM 3,300,000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>City Of Dreams, Tanjong Tokong</t>
+          <t>One Tanjong, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/city-of-dreams-seaview-condo-1185sf-fully-furnished-115000031.htm</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>14</v>
-      </c>
+          <t>https://www.mudah.my/luxury-apartment-with-unobstructed-sea-view-best-price-on-the-market-115022080.htm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 weeks ago | RM 1,227,000 | City Of Dreams, Tanjong Tokong |  | 1,185 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | City of Dreams Seaview Condo 1185sf Fully Furnished</t>
+          <t>Condominium For Sale | 1w | RM 3,300,000 | One Tanjong, Tanjung Bungah |  | 4,756 |  | sq.ft |  | 5 |  | Bed |  | 5 |  | Bath |  | Freehold |  | Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
+          <t>The Tamarind, walking distance to Stonyhurst International School</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1037,57 +991,51 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RM 4,800,000</t>
+          <t>RM 799,000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Springtide Residences, Tanjung Bungah</t>
+          <t>The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/springtide-residences-beachfront-luxury-condominium-in-tanjung-bungah-115100943.htm</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>7</v>
-      </c>
+          <t>https://www.mudah.my/the-tamarind-walking-distance-to-stonyhurst-international-school-115026766.htm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
+          <t>Condominium For Sale | 1w | RM 799,000 | The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong |  | 1,047 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Tamarind, walking distance to Stonyhurst International School</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Santorini renovated</t>
+          <t>Twin Towers Condo, Tg Bungah</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1097,12 +1045,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RM 530,000</t>
+          <t>RM 600,000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>I-Santorini, Tanjong Tokong</t>
+          <t>Twin Towers, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1117,52 +1065,46 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/santorini-renovated-115045187.htm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>7</v>
-      </c>
+          <t>https://www.mudah.my/twin-towers-condo-tg-bungah-115027655.htm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 530,000 | I-Santorini, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Santorini renovated</t>
+          <t>Condominium For Sale | 1w | RM 600,000 | Twin Towers, Tanjung Bungah |  | 1,300 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Towers Condo, Tg Bungah</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Taman Skyridge Apartment</t>
+          <t>City of Dreams Seaview Condo 1185sf Fully Furnished</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RM 530,000</t>
+          <t>RM 1,227,000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Skyridge Apartment, Tanjong Tokong</t>
+          <t>City Of Dreams, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1177,37 +1119,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/taman-skyridge-apartment-115060516.htm</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>7</v>
-      </c>
+          <t>https://www.mudah.my/city-of-dreams-seaview-condo-1185sf-fully-furnished-115000031.htm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 1 week ago | RM 530,000 | Skyridge Apartment, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Taman Skyridge Apartment</t>
+          <t>Condominium For Sale | 2w | RM 1,227,000 | City Of Dreams, Tanjong Tokong |  | 1,185 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | City of Dreams Seaview Condo 1185sf Fully Furnished</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>The Tamarind, walking distance to Stonyhurst International School</t>
+          <t>Twin Tower Condo Tanjung Bunga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1217,12 +1153,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RM 799,000</t>
+          <t>RM 565,000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong</t>
+          <t>Twin Towers, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1237,37 +1173,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-tamarind-walking-distance-to-stonyhurst-international-school-115026766.htm</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>7</v>
-      </c>
+          <t>https://www.mudah.my/twin-tower-condo-tanjung-bunga-114995728.htm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 799,000 | The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong |  | 1,047 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Tamarind, walking distance to Stonyhurst International School</t>
+          <t>Condominium For Sale | 2w | RM 565,000 | Twin Towers, Tanjung Bungah |  | 1,248 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Tower Condo Tanjung Bunga</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
+          <t>Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1277,57 +1207,51 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RM 3,300,000</t>
+          <t>RM 415,000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>One Tanjong, Tanjung Bungah</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/luxury-apartment-with-unobstructed-sea-view-best-price-on-the-market-115022080.htm</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>7</v>
-      </c>
+          <t>https://www.mudah.my/tri-pinnacle-condo-tanjong-tokong-800sf-for-sale-original-unit-114993450.htm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 3,300,000 | One Tanjong, Tanjung Bungah |  | 4,756 |  | sq.ft |  | 5 |  | Bed |  | 5 |  | Bath |  | Freehold |  | Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
+          <t>Condominium For Sale | 2w | RM 415,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Twin Towers Condo, Tg Bungah</t>
+          <t>Furnished with nice seaview</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1337,7 +1261,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RM 600,000</t>
+          <t>RM 380,000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1347,7 +1271,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1357,52 +1281,46 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>926</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/twin-towers-condo-tg-bungah-115027655.htm</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>7</v>
-      </c>
+          <t>https://www.mudah.my/furnished-with-nice-seaview-114995729.htm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 600,000 | Twin Towers, Tanjung Bungah |  | 1,300 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Towers Condo, Tg Bungah</t>
+          <t>Condominium For Sale | 2w | RM 380,000 | Twin Towers, Tanjung Bungah |  | 926 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Furnished with nice seaview</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Quiet Townhouse with Seaview</t>
+          <t>Puncak Erskine 88 Full Furnished &amp; Renovated</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RM 580,000</t>
+          <t>RM 180,000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tanjung Bungah, Penang</t>
+          <t>Puncak Erskine, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1412,57 +1330,51 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>650</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/quiet-townhouse-with-seaview-115045058.htm</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>7</v>
-      </c>
+          <t>https://www.mudah.my/puncak-erskine-88-full-furnished-renovated-115022482.htm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Townhouse For Sale | listed 1 week ago | RM 580,000 | Tanjung Bungah, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Quiet Townhouse with Seaview</t>
+          <t>Apartment For Sale | 2w | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Puncak Erskine 88 Full Furnished &amp; Renovated</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tri pinnacle tanjung tokong</t>
+          <t>1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>1.5-storey Terraced House</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RM 450,000</t>
+          <t>RM 899,000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>Tanjong Tokong, Penang</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1477,112 +1389,92 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-115045263.htm</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>7</v>
-      </c>
+          <t>https://www.mudah.my/1-5-storey-terraced-house-tanjung-tokong-near-straight-quay-gurney-114981119.htm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 week ago | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong</t>
+          <t>1.5-storey Terraced House For Sale | 2w | RM 899,000 | Tanjong Tokong, Penang |  | 1,900 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | 1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3 bedrooms 2 bathrooms 2 car park for sale</t>
+          <t>Island 88 Shoplot (1st Floor)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Shop lot</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RM 608,000</t>
+          <t>RM 689,000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>I-Santorini, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Tanjong Tokong, Penang</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>930</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/3-bedrooms-2-bathrooms-2-car-park-for-sale-115083940.htm</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>5</v>
-      </c>
+          <t>https://www.mudah.my/island-88-shoplot-1st-floor-114982296.htm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 5 days ago | RM 608,000 | I-Santorini, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | 3 bedrooms 2 bathrooms 2 car park for sale</t>
+          <t>Shop lot For Sale | 2w | RM 689,000 | Tanjong Tokong, Penang |  | 930 |  | sq.ft |  | Freehold |  | Island 88 Shoplot (1st Floor)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Below Market Attractive Unit</t>
+          <t>The Peak Resident Condominium</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RM 340,000</t>
+          <t>RM 638,000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>The Peak Residences, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1597,37 +1489,31 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/below-market-attractive-unit-115034831.htm</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>5</v>
-      </c>
+          <t>https://www.mudah.my/the-peak-resident-condominium-114960623.htm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 5 days ago | RM 340,000 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Below Market Attractive Unit</t>
+          <t>Condominium For Sale | 2w | RM 638,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Resident Condominium</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>An airy and pleasant unit on the top most floor with scenic views</t>
+          <t>Below Market Attractive Unit</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1637,12 +1523,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RM 299,950</t>
+          <t>RM 340,000</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Taman Kristal, Tanjong Tokong</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1657,157 +1543,139 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>650</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/an-airy-and-pleasant-unit-on-the-top-most-floor-with-scenic-views-114303816.htm</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>5</v>
-      </c>
+          <t>https://www.mudah.my/below-market-attractive-unit-115034831.htm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 5 days ago | RM 299,950 | Taman Kristal, Tanjong Tokong |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | An airy and pleasant unit on the top most floor with scenic views</t>
+          <t>Apartment For Sale | 5d | RM 340,000 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Below Market Attractive Unit</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Straits Residence one of the best Investment</t>
+          <t>3 bedrooms 2 bathrooms 2 car park for sale</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Service Residence</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RM 2,500,000</t>
+          <t>RM 608,000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Straits Quay, Tanjong Tokong</t>
+          <t>I-Santorini, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/straits-residence-one-of-the-best-investment-115089396.htm</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>4</v>
-      </c>
+          <t>https://www.mudah.my/3-bedrooms-2-bathrooms-2-car-park-for-sale-115083940.htm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Service Residence For Sale | listed 4 days ago | RM 2,500,000 | Straits Quay, Tanjong Tokong |  | 1,296 |  | sq.ft |  | 2 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Straits Residence one of the best Investment</t>
+          <t>Condominium For Sale | 5d | RM 608,000 | I-Santorini, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | 3 bedrooms 2 bathrooms 2 car park for sale</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Apartment For Sale</t>
+          <t>Straits Residence one of the best Investment</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Service Residence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RM 180,000</t>
+          <t>RM 2,500,000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Puncak Erskine, Tanjong Tokong</t>
+          <t>Straits Quay, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/apartment-for-sale-115093031.htm</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>4</v>
-      </c>
+          <t>https://www.mudah.my/straits-residence-one-of-the-best-investment-115089396.htm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 4 days ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 1 |  | Bath |  | Freehold |  | Apartment For Sale</t>
+          <t>Service Residence For Sale | 4d | RM 2,500,000 | Straits Quay, Tanjong Tokong |  | 1,296 |  | sq.ft |  | 2 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Straits Residence one of the best Investment</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The peak RENO to TWO room</t>
+          <t>Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1817,17 +1685,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RM 528,000</t>
+          <t>RM 353,800</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>The Peak Residences, Tanjong Tokong</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1837,37 +1705,31 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>650</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-peak-reno-to-two-room-115092789.htm</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>4</v>
-      </c>
+          <t>https://www.mudah.my/tg-tokong-apartment-fully-furnished-with-2-carparks-115129412.htm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 4 days ago | RM 528,000 | The Peak Residences, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The peak RENO to TWO room</t>
+          <t>Condominium For Sale | 3d | RM 353,800 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>The Peak Condominium</t>
+          <t>Looking For Investors Only</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1877,17 +1739,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RM 530,000</t>
+          <t>RM 598,888</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The Peak Residences, Tanjong Tokong</t>
+          <t>Marine Mansion, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1897,37 +1759,31 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>850</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-peak-condominium-115093455.htm</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>4</v>
-      </c>
+          <t>https://www.mudah.my/looking-for-investors-only-115155444.htm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 4 days ago | RM 530,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Condominium</t>
+          <t>Condominium For Sale | 5h | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
+          <t>Looking For Investors Only</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1937,17 +1793,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RM 500,000</t>
+          <t>RM 888,888</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>Desa Mas (Pulau Tikus), Pulau Tikus</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1957,37 +1813,31 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-jalan-persiaran-halia-3-tanjung-tokong-115090201.htm</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>4</v>
-      </c>
+          <t>https://www.mudah.my/looking-for-investors-only-115155435.htm</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 4 days ago | RM 500,000 | Tri Pinnacle, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
+          <t>Condominium For Sale | 5h | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E Garden apartment for sale</t>
+          <t>[RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1997,12 +1847,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RM 342,000</t>
+          <t>RM 360,000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>E Garden, Tanjong Tokong</t>
+          <t>Skyridge Apartment, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2017,57 +1867,51 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>750</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/e-garden-apartment-for-sale-115127752.htm</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>3</v>
-      </c>
+          <t>https://www.mudah.my/rare-unit-skyridge-apartment-for-sales-tanjong-tokong-gurney-115113858.htm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 3 days ago | RM 342,000 | E Garden, Tanjong Tokong |  | 760 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | E Garden apartment for sale</t>
+          <t>Apartment For Sale | 1d | RM 360,000 | Skyridge Apartment, Tanjong Tokong |  | 750 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | [RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Single Storey Semi D House Hillside,Tanjung Bungah,Penang.</t>
+          <t>Azuria Condominium - Direct Owner</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Semi-Detached House</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RM 1,650,000</t>
+          <t>RM 335,000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tanjung Bungah, Penang</t>
+          <t>Azuria, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2077,37 +1921,31 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/single-storey-semi-d-house-hillside-tanjung-bungah-penang-113480651.htm</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>3</v>
-      </c>
+          <t>https://www.mudah.my/azuria-condominium-direct-owner-111620926.htm</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Semi-Detached House For Sale | listed 3 days ago | RM 1,650,000 | Tanjung Bungah, Penang |  | 4,395 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Single Storey Semi D House Hillside,Tanjung Bungah,Penang.</t>
+          <t>Condominium For Sale | 1d | RM 335,000 | Azuria, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Azuria Condominium - Direct Owner</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tanjong Bungah Hillside Garden Apartment For Sale.</t>
+          <t>Marine Mansion</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2117,12 +1955,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RM 368,000</t>
+          <t>RM 600,000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tanjung Bungah</t>
+          <t>Marine Mansion, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2137,57 +1975,51 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>850</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tanjong-bungah-hillside-garden-apartment-for-sale-114853211.htm</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>3</v>
-      </c>
+          <t>https://www.mudah.my/marine-mansion-115137839.htm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 3 days ago | RM 368,000 | 5% | RM 388,000 | Hillside Garden, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tanjong Bungah Hillside Garden Apartment For Sale.</t>
+          <t>Condominium For Sale | 2d | RM 600,000 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Marine Mansion</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
+          <t>Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1-storey Terraced House</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RM 410,000</t>
+          <t>RM 1,200,000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tanjong Tokong, Penang</t>
+          <t>Quayside, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2197,37 +2029,31 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/taman-intan-delima-single-storey-terrace-batu-kawan-freehold-115126865.htm</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>3</v>
-      </c>
+          <t>https://www.mudah.my/pinang-quayside-condo-fully-furnished-1bedroom-2-bathrooms-unit-103758517.htm</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1-storey Terraced House For Sale | listed 3 days ago | RM 410,000 | Tanjong Tokong, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
+          <t>Condominium For Sale | 2d | RM 1,200,000 | Quayside, Tanjong Tokong |  | 1,137 |  | sq.ft |  | 1 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
+          <t>Tanjong Bungah Hillside Garden Apartment For Sale.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2237,12 +2063,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RM 538,000</t>
+          <t>RM 368,000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>I-Santorini, Tanjong Tokong</t>
+          <t>Tanjung Bungah</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2257,47 +2083,41 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/direct-owner-fully-furnished-nice-santorini-with-3-carparks-115127587.htm</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
+          <t>https://www.mudah.my/tanjong-bungah-hillside-garden-apartment-for-sale-114853211.htm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 3 days ago | RM 538,000 | I-Santorini, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
+          <t>Condominium For Sale | 3d | RM 368,000 | 5% | RM 388,000 | Hillside Garden, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tanjong Bungah Hillside Garden Apartment For Sale.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>House for sale</t>
+          <t>Single Storey Semi D House Hillside,Tanjung Bungah,Penang.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Semi-Detached House</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RM 760,000</t>
+          <t>RM 1,650,000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2307,7 +2127,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2317,52 +2137,46 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/house-for-sale-108064933.htm</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>3</v>
-      </c>
+          <t>https://www.mudah.my/single-storey-semi-d-house-hillside-tanjung-bungah-penang-113480651.htm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Townhouse For Sale | listed 3 days ago | RM 760,000 | Tanjung Bungah, Penang |  | 1,200 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | House for sale</t>
+          <t>Semi-Detached House For Sale | 3d | RM 1,650,000 | Tanjung Bungah, Penang |  | 4,395 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Single Storey Semi D House Hillside,Tanjung Bungah,Penang.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
+          <t>Apartment For Sale</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RM 353,800</t>
+          <t>RM 180,000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>Puncak Erskine, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2372,62 +2186,56 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tg-tokong-apartment-fully-furnished-with-2-carparks-115129412.htm</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>3</v>
-      </c>
+          <t>https://www.mudah.my/apartment-for-sale-115093031.htm</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 3 days ago | RM 353,800 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
+          <t>Apartment For Sale | 4d | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 1 |  | Bath |  | Freehold |  | Apartment For Sale</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
+          <t>E Garden apartment for sale</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RM 1,200,000</t>
+          <t>RM 342,000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Quayside, Tanjong Tokong</t>
+          <t>E Garden, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2437,37 +2245,31 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/pinang-quayside-condo-fully-furnished-1bedroom-2-bathrooms-unit-103758517.htm</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
+          <t>https://www.mudah.my/e-garden-apartment-for-sale-115127752.htm</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 days ago | RM 1,200,000 | Quayside, Tanjong Tokong |  | 1,137 |  | sq.ft |  | 1 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
+          <t>Apartment For Sale | 3d | RM 342,000 | E Garden, Tanjong Tokong |  | 760 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | E Garden apartment for sale</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marine Mansion</t>
+          <t>Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2477,12 +2279,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RM 600,000</t>
+          <t>RM 538,000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Marine Mansion, Tanjung Bungah</t>
+          <t>I-Santorini, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2502,47 +2304,41 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/marine-mansion-115137839.htm</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
+          <t>https://www.mudah.my/direct-owner-fully-furnished-nice-santorini-with-3-carparks-115127587.htm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 days ago | RM 600,000 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Marine Mansion</t>
+          <t>Condominium For Sale | 3d | RM 538,000 | I-Santorini, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azuria Condominium - Direct Owner</t>
+          <t>TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>1-storey Terraced House</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RM 335,000</t>
+          <t>RM 410,000</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Azuria, Tanjung Bungah</t>
+          <t>Tanjong Tokong, Penang</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2557,52 +2353,46 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/azuria-condominium-direct-owner-111620926.htm</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
+          <t>https://www.mudah.my/taman-intan-delima-single-storey-terrace-batu-kawan-freehold-115126865.htm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 1 day ago | RM 335,000 | Azuria, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Azuria Condominium - Direct Owner</t>
+          <t>1-storey Terraced House For Sale | 3d | RM 410,000 | Tanjong Tokong, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
+          <t>House for sale</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RM 360,000</t>
+          <t>RM 760,000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Skyridge Apartment, Tanjong Tokong</t>
+          <t>Tanjung Bungah, Penang</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2617,37 +2407,31 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/rare-unit-skyridge-apartment-for-sales-tanjong-tokong-gurney-115113858.htm</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
+          <t>https://www.mudah.my/house-for-sale-108064933.htm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Apartment For Sale | listed 1 day ago | RM 360,000 | Skyridge Apartment, Tanjong Tokong |  | 750 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | [RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
+          <t>Townhouse For Sale | 3d | RM 760,000 | Tanjung Bungah, Penang |  | 1,200 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | House for sale</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Andaman</t>
+          <t>The Peak Condominium</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2657,12 +2441,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RM 4,000,000</t>
+          <t>RM 530,000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>18 East @ Andaman, Tanjong Tokong</t>
+          <t>The Peak Residences, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2672,42 +2456,36 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/andaman-115157424.htm</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
+          <t>https://www.mudah.my/the-peak-condominium-115093455.htm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 2 hours ago | RM 4,000,000 | 18 East @ Andaman, Tanjong Tokong |  | 2,827 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Andaman</t>
+          <t>Condominium For Sale | 4d | RM 530,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Condominium</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>city of dream condominiums house gurney sea view</t>
+          <t>TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2717,17 +2495,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RM 15,933,500</t>
+          <t>RM 500,000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>City Of Dreams, Tanjong Tokong</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2737,37 +2515,31 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>850</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/city-of-dream-condominiums-house-gurney-sea-view-115155857.htm</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
+          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-jalan-persiaran-halia-3-tanjung-tokong-115090201.htm</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 4 hours ago | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view</t>
+          <t>Condominium For Sale | 4d | RM 500,000 | Tri Pinnacle, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Looking For Investors Only</t>
+          <t>The peak RENO to TWO room</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2777,17 +2549,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RM 598,888</t>
+          <t>RM 528,000</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Marine Mansion, Tanjung Bungah</t>
+          <t>The Peak Residences, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2797,37 +2569,31 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/looking-for-investors-only-115155444.htm</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
+          <t>https://www.mudah.my/the-peak-reno-to-two-room-115092789.htm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 5 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+          <t>Condominium For Sale | 4d | RM 528,000 | The Peak Residences, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The peak RENO to TWO room</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Looking For Investors Only</t>
+          <t>TRI Pinnacle</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2837,17 +2603,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RM 888,888</t>
+          <t>RM 550,000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Desa Mas (Pulau Tikus), Pulau Tikus</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2857,30 +2623,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/looking-for-investors-only-115155435.htm</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
+          <t>https://www.mudah.my/tri-pinnacle-114681845.htm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Condominium For Sale | listed 5 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+          <t>Condominium For Sale | 2w | RM 550,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI Pinnacle</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-02 08:30</t>
+          <t>2026-07-02 08:35</t>
         </is>
       </c>
     </row>

--- a/scripts/mudah-penang-scraper/penang_listings.xlsx
+++ b/scripts/mudah-penang-scraper/penang_listings.xlsx
@@ -495,7 +495,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Andaman</t>
+          <t>TRI Pinnacle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -505,12 +505,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RM 4,000,000</t>
+          <t>RM 550,000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18 East @ Andaman, Tanjong Tokong</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,36 +520,42 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/andaman-115157424.htm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>https://www.mudah.my/tri-pinnacle-114681845.htm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>14</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 2h | RM 4,000,000 | 18 East @ Andaman, Tanjong Tokong |  | 2,827 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Andaman</t>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 550,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI Pinnacle</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>city of dream condominiums house gurney sea view</t>
+          <t>The Peak Resident Condominium</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -559,17 +565,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RM 15,933,500</t>
+          <t>RM 638,000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>City Of Dreams, Tanjong Tokong</t>
+          <t>The Peak Residences, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -579,139 +585,149 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/city-of-dream-condominiums-house-gurney-sea-view-115155857.htm</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>https://www.mudah.my/the-peak-resident-condominium-114960623.htm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>14</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 4h | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view</t>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 638,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Resident Condominium</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>An airy and pleasant unit on the top most floor with scenic views</t>
+          <t>Island 88 Shoplot (1st Floor)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Shop lot</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RM 299,950</t>
+          <t>RM 689,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Taman Kristal, Tanjong Tokong</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Tanjong Tokong, Penang</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>930</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/an-airy-and-pleasant-unit-on-the-top-most-floor-with-scenic-views-114303816.htm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>https://www.mudah.my/island-88-shoplot-1st-floor-114982296.htm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Apartment For Sale | 5d | RM 299,950 | Taman Kristal, Tanjong Tokong |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | An airy and pleasant unit on the top most floor with scenic views</t>
+          <t>Shop lot For Sale | listed 2 weeks ago | RM 689,000 | Tanjong Tokong, Penang |  | 930 |  | sq.ft |  | Freehold |  | Island 88 Shoplot (1st Floor)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
+          <t>1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>1.5-storey Terraced House</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RM 4,800,000</t>
+          <t>RM 899,000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Springtide Residences, Tanjung Bungah</t>
+          <t>Tanjong Tokong, Penang</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/springtide-residences-beachfront-luxury-condominium-in-tanjung-bungah-115100943.htm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>https://www.mudah.my/1-5-storey-terraced-house-tanjung-tokong-near-straight-quay-gurney-114981119.htm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 1w | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
+          <t>1.5-storey Terraced House For Sale | listed 2 weeks ago | RM 899,000 | Tanjong Tokong, Penang |  | 1,900 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | 1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Taman Skyridge Apartment</t>
+          <t>Puncak Erskine 88 Full Furnished &amp; Renovated</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -721,12 +737,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RM 530,000</t>
+          <t>RM 180,000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Skyridge Apartment, Tanjong Tokong</t>
+          <t>Puncak Erskine, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -736,56 +752,62 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>650</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/taman-skyridge-apartment-115060516.htm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>https://www.mudah.my/puncak-erskine-88-full-furnished-renovated-115022482.htm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>14</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Apartment For Sale | 1w | RM 530,000 | Skyridge Apartment, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Taman Skyridge Apartment</t>
+          <t>Apartment For Sale | listed 2 weeks ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Puncak Erskine 88 Full Furnished &amp; Renovated</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Quiet Townhouse with Seaview</t>
+          <t>Furnished with nice seaview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RM 580,000</t>
+          <t>RM 380,000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tanjung Bungah, Penang</t>
+          <t>Twin Towers, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -795,31 +817,37 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>926</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/quiet-townhouse-with-seaview-115045058.htm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>https://www.mudah.my/furnished-with-nice-seaview-114995729.htm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>14</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Townhouse For Sale | 1w | RM 580,000 | Tanjung Bungah, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Quiet Townhouse with Seaview</t>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 380,000 | Twin Towers, Tanjung Bungah |  | 926 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Furnished with nice seaview</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Santorini renovated</t>
+          <t>Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -829,12 +857,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RM 530,000</t>
+          <t>RM 415,000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>I-Santorini, Tanjong Tokong</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -849,31 +877,37 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/santorini-renovated-115045187.htm</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>https://www.mudah.my/tri-pinnacle-condo-tanjong-tokong-800sf-for-sale-original-unit-114993450.htm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>14</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 1w | RM 530,000 | I-Santorini, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Santorini renovated</t>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 415,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tri pinnacle tanjung tokong</t>
+          <t>Twin Tower Condo Tanjung Bunga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -883,12 +917,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RM 450,000</t>
+          <t>RM 565,000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>Twin Towers, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -903,31 +937,37 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-115045263.htm</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>https://www.mudah.my/twin-tower-condo-tanjung-bunga-114995728.htm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>14</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 1w | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong</t>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 565,000 | Twin Towers, Tanjung Bungah |  | 1,248 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Tower Condo Tanjung Bunga</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
+          <t>City of Dreams Seaview Condo 1185sf Fully Furnished</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -937,51 +977,57 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RM 3,300,000</t>
+          <t>RM 1,227,000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>One Tanjong, Tanjung Bungah</t>
+          <t>City Of Dreams, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/luxury-apartment-with-unobstructed-sea-view-best-price-on-the-market-115022080.htm</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>https://www.mudah.my/city-of-dreams-seaview-condo-1185sf-fully-furnished-115000031.htm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>14</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 1w | RM 3,300,000 | One Tanjong, Tanjung Bungah |  | 4,756 |  | sq.ft |  | 5 |  | Bed |  | 5 |  | Bath |  | Freehold |  | Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
+          <t>Condominium For Sale | listed 2 weeks ago | RM 1,227,000 | City Of Dreams, Tanjong Tokong |  | 1,185 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | City of Dreams Seaview Condo 1185sf Fully Furnished</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>The Tamarind, walking distance to Stonyhurst International School</t>
+          <t>Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -991,51 +1037,57 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RM 799,000</t>
+          <t>RM 4,800,000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong</t>
+          <t>Springtide Residences, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-tamarind-walking-distance-to-stonyhurst-international-school-115026766.htm</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>https://www.mudah.my/springtide-residences-beachfront-luxury-condominium-in-tanjung-bungah-115100943.htm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 1w | RM 799,000 | The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong |  | 1,047 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Tamarind, walking distance to Stonyhurst International School</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 4,800,000 | Springtide Residences, Tanjung Bungah |  | 5,221 |  | sq.ft |  | 5 |  | Bed |  | 7 |  | Bath |  | Freehold |  | Springtide Residences Beachfront Luxury Condominium in Tanjung Bungah</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Twin Towers Condo, Tg Bungah</t>
+          <t>Santorini renovated</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1045,12 +1097,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RM 600,000</t>
+          <t>RM 530,000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Twin Towers, Tanjung Bungah</t>
+          <t>I-Santorini, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1065,46 +1117,52 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/twin-towers-condo-tg-bungah-115027655.htm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>https://www.mudah.my/santorini-renovated-115045187.htm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 1w | RM 600,000 | Twin Towers, Tanjung Bungah |  | 1,300 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Towers Condo, Tg Bungah</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 530,000 | I-Santorini, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Santorini renovated</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>City of Dreams Seaview Condo 1185sf Fully Furnished</t>
+          <t>Taman Skyridge Apartment</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RM 1,227,000</t>
+          <t>RM 530,000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>City Of Dreams, Tanjong Tokong</t>
+          <t>Skyridge Apartment, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1119,31 +1177,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>850</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/city-of-dreams-seaview-condo-1185sf-fully-furnished-115000031.htm</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>https://www.mudah.my/taman-skyridge-apartment-115060516.htm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 2w | RM 1,227,000 | City Of Dreams, Tanjong Tokong |  | 1,185 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | City of Dreams Seaview Condo 1185sf Fully Furnished</t>
+          <t>Apartment For Sale | listed 1 week ago | RM 530,000 | Skyridge Apartment, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Taman Skyridge Apartment</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Twin Tower Condo Tanjung Bunga</t>
+          <t>The Tamarind, walking distance to Stonyhurst International School</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1153,12 +1217,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RM 565,000</t>
+          <t>RM 799,000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Twin Towers, Tanjung Bungah</t>
+          <t>The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1173,31 +1237,37 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/twin-tower-condo-tanjung-bunga-114995728.htm</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>https://www.mudah.my/the-tamarind-walking-distance-to-stonyhurst-international-school-115026766.htm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 2w | RM 565,000 | Twin Towers, Tanjung Bungah |  | 1,248 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Tower Condo Tanjung Bunga</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 799,000 | The Tamarind @ Seri Tanjung Pinang, Tanjong Tokong |  | 1,047 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Tamarind, walking distance to Stonyhurst International School</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
+          <t>Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1207,51 +1277,57 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RM 415,000</t>
+          <t>RM 3,300,000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>One Tanjong, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-condo-tanjong-tokong-800sf-for-sale-original-unit-114993450.htm</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>https://www.mudah.my/luxury-apartment-with-unobstructed-sea-view-best-price-on-the-market-115022080.htm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 2w | RM 415,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tri Pinnacle Condo Tanjong Tokong 800sf For Sale original unit</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 3,300,000 | One Tanjong, Tanjung Bungah |  | 4,756 |  | sq.ft |  | 5 |  | Bed |  | 5 |  | Bath |  | Freehold |  | Luxury Apartment with Unobstructed Sea View – Best Price on the Market</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Furnished with nice seaview</t>
+          <t>Twin Towers Condo, Tg Bungah</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1261,7 +1337,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RM 380,000</t>
+          <t>RM 600,000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1271,7 +1347,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1281,46 +1357,52 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/furnished-with-nice-seaview-114995729.htm</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>https://www.mudah.my/twin-towers-condo-tg-bungah-115027655.htm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 2w | RM 380,000 | Twin Towers, Tanjung Bungah |  | 926 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Furnished with nice seaview</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 600,000 | Twin Towers, Tanjung Bungah |  | 1,300 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Twin Towers Condo, Tg Bungah</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Puncak Erskine 88 Full Furnished &amp; Renovated</t>
+          <t>Quiet Townhouse with Seaview</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RM 180,000</t>
+          <t>RM 580,000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Puncak Erskine, Tanjong Tokong</t>
+          <t>Tanjung Bungah, Penang</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1330,51 +1412,57 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/puncak-erskine-88-full-furnished-renovated-115022482.htm</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>https://www.mudah.my/quiet-townhouse-with-seaview-115045058.htm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Apartment For Sale | 2w | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Puncak Erskine 88 Full Furnished &amp; Renovated</t>
+          <t>Townhouse For Sale | listed 1 week ago | RM 580,000 | Tanjung Bungah, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Quiet Townhouse with Seaview</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
+          <t>tri pinnacle tanjung tokong</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.5-storey Terraced House</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RM 899,000</t>
+          <t>RM 450,000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tanjong Tokong, Penang</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1389,92 +1477,112 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/1-5-storey-terraced-house-tanjung-tokong-near-straight-quay-gurney-114981119.htm</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-115045263.htm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.5-storey Terraced House For Sale | 2w | RM 899,000 | Tanjong Tokong, Penang |  | 1,900 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | 1.5 storey Terraced House (Tanjung Tokong) near Straight Quay, gurney</t>
+          <t>Condominium For Sale | listed 1 week ago | RM 450,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | tri pinnacle tanjung tokong</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Island 88 Shoplot (1st Floor)</t>
+          <t>3 bedrooms 2 bathrooms 2 car park for sale</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shop lot</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RM 689,000</t>
+          <t>RM 608,000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tanjong Tokong, Penang</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+          <t>I-Santorini, Tanjong Tokong</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/island-88-shoplot-1st-floor-114982296.htm</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>https://www.mudah.my/3-bedrooms-2-bathrooms-2-car-park-for-sale-115083940.htm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Shop lot For Sale | 2w | RM 689,000 | Tanjong Tokong, Penang |  | 930 |  | sq.ft |  | Freehold |  | Island 88 Shoplot (1st Floor)</t>
+          <t>Condominium For Sale | listed 5 days ago | RM 608,000 | I-Santorini, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | 3 bedrooms 2 bathrooms 2 car park for sale</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>The Peak Resident Condominium</t>
+          <t>Below Market Attractive Unit</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RM 638,000</t>
+          <t>RM 340,000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>The Peak Residences, Tanjong Tokong</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1489,31 +1597,37 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>650</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-peak-resident-condominium-114960623.htm</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>https://www.mudah.my/below-market-attractive-unit-115034831.htm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 2w | RM 638,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Resident Condominium</t>
+          <t>Apartment For Sale | listed 5 days ago | RM 340,000 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Below Market Attractive Unit</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Below Market Attractive Unit</t>
+          <t>An airy and pleasant unit on the top most floor with scenic views</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1523,12 +1637,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RM 340,000</t>
+          <t>RM 299,950</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>Taman Kristal, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1543,139 +1657,157 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/below-market-attractive-unit-115034831.htm</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>https://www.mudah.my/an-airy-and-pleasant-unit-on-the-top-most-floor-with-scenic-views-114303816.htm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Apartment For Sale | 5d | RM 340,000 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Below Market Attractive Unit</t>
+          <t>Apartment For Sale | listed 5 days ago | RM 299,950 | Taman Kristal, Tanjong Tokong |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | An airy and pleasant unit on the top most floor with scenic views</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3 bedrooms 2 bathrooms 2 car park for sale</t>
+          <t>Straits Residence one of the best Investment</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Service Residence</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RM 608,000</t>
+          <t>RM 2,500,000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>I-Santorini, Tanjong Tokong</t>
+          <t>Straits Quay, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/3-bedrooms-2-bathrooms-2-car-park-for-sale-115083940.htm</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>https://www.mudah.my/straits-residence-one-of-the-best-investment-115089396.htm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 5d | RM 608,000 | I-Santorini, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | 3 bedrooms 2 bathrooms 2 car park for sale</t>
+          <t>Service Residence For Sale | listed 4 days ago | RM 2,500,000 | Straits Quay, Tanjong Tokong |  | 1,296 |  | sq.ft |  | 2 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Straits Residence one of the best Investment</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Straits Residence one of the best Investment</t>
+          <t>Apartment For Sale</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Service Residence</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RM 2,500,000</t>
+          <t>RM 180,000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Straits Quay, Tanjong Tokong</t>
+          <t>Puncak Erskine, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/straits-residence-one-of-the-best-investment-115089396.htm</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>https://www.mudah.my/apartment-for-sale-115093031.htm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Service Residence For Sale | 4d | RM 2,500,000 | Straits Quay, Tanjong Tokong |  | 1,296 |  | sq.ft |  | 2 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Straits Residence one of the best Investment</t>
+          <t>Apartment For Sale | listed 4 days ago | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 1 |  | Bath |  | Freehold |  | Apartment For Sale</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
+          <t>The peak RENO to TWO room</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1685,17 +1817,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RM 353,800</t>
+          <t>RM 528,000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>The Peak Residences, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1705,31 +1837,37 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tg-tokong-apartment-fully-furnished-with-2-carparks-115129412.htm</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>https://www.mudah.my/the-peak-reno-to-two-room-115092789.htm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 3d | RM 353,800 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
+          <t>Condominium For Sale | listed 4 days ago | RM 528,000 | The Peak Residences, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The peak RENO to TWO room</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Looking For Investors Only</t>
+          <t>The Peak Condominium</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1739,17 +1877,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RM 598,888</t>
+          <t>RM 530,000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Marine Mansion, Tanjung Bungah</t>
+          <t>The Peak Residences, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1759,31 +1897,37 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/looking-for-investors-only-115155444.htm</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>https://www.mudah.my/the-peak-condominium-115093455.htm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 5h | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+          <t>Condominium For Sale | listed 4 days ago | RM 530,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Condominium</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Looking For Investors Only</t>
+          <t>TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1793,17 +1937,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RM 888,888</t>
+          <t>RM 500,000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Desa Mas (Pulau Tikus), Pulau Tikus</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1813,31 +1957,37 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>850</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/looking-for-investors-only-115155435.htm</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-jalan-persiaran-halia-3-tanjung-tokong-115090201.htm</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 5h | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
+          <t>Condominium For Sale | listed 4 days ago | RM 500,000 | Tri Pinnacle, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
+          <t>E Garden apartment for sale</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1847,12 +1997,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RM 360,000</t>
+          <t>RM 342,000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Skyridge Apartment, Tanjong Tokong</t>
+          <t>E Garden, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1867,51 +2017,57 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/rare-unit-skyridge-apartment-for-sales-tanjong-tokong-gurney-115113858.htm</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>https://www.mudah.my/e-garden-apartment-for-sale-115127752.htm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Apartment For Sale | 1d | RM 360,000 | Skyridge Apartment, Tanjong Tokong |  | 750 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | [RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
+          <t>Apartment For Sale | listed 3 days ago | RM 342,000 | E Garden, Tanjong Tokong |  | 760 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | E Garden apartment for sale</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azuria Condominium - Direct Owner</t>
+          <t>Single Storey Semi D House Hillside,Tanjung Bungah,Penang.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>Semi-Detached House</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RM 335,000</t>
+          <t>RM 1,650,000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Azuria, Tanjung Bungah</t>
+          <t>Tanjung Bungah, Penang</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1921,31 +2077,37 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/azuria-condominium-direct-owner-111620926.htm</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>https://www.mudah.my/single-storey-semi-d-house-hillside-tanjung-bungah-penang-113480651.htm</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 1d | RM 335,000 | Azuria, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Azuria Condominium - Direct Owner</t>
+          <t>Semi-Detached House For Sale | listed 3 days ago | RM 1,650,000 | Tanjung Bungah, Penang |  | 4,395 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Single Storey Semi D House Hillside,Tanjung Bungah,Penang.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marine Mansion</t>
+          <t>Tanjong Bungah Hillside Garden Apartment For Sale.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1955,12 +2117,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RM 600,000</t>
+          <t>RM 368,000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Marine Mansion, Tanjung Bungah</t>
+          <t>Tanjung Bungah</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1975,51 +2137,57 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/marine-mansion-115137839.htm</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>https://www.mudah.my/tanjong-bungah-hillside-garden-apartment-for-sale-114853211.htm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 2d | RM 600,000 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Marine Mansion</t>
+          <t>Condominium For Sale | listed 3 days ago | RM 368,000 | 5% | RM 388,000 | Hillside Garden, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tanjong Bungah Hillside Garden Apartment For Sale.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
+          <t>TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Condominium</t>
+          <t>1-storey Terraced House</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RM 1,200,000</t>
+          <t>RM 410,000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Quayside, Tanjong Tokong</t>
+          <t>Tanjong Tokong, Penang</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2029,31 +2197,37 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/pinang-quayside-condo-fully-furnished-1bedroom-2-bathrooms-unit-103758517.htm</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>https://www.mudah.my/taman-intan-delima-single-storey-terrace-batu-kawan-freehold-115126865.htm</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 2d | RM 1,200,000 | Quayside, Tanjong Tokong |  | 1,137 |  | sq.ft |  | 1 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
+          <t>1-storey Terraced House For Sale | listed 3 days ago | RM 410,000 | Tanjong Tokong, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tanjong Bungah Hillside Garden Apartment For Sale.</t>
+          <t>Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2063,12 +2237,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RM 368,000</t>
+          <t>RM 538,000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tanjung Bungah</t>
+          <t>I-Santorini, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2083,41 +2257,47 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>850</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tanjong-bungah-hillside-garden-apartment-for-sale-114853211.htm</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>https://www.mudah.my/direct-owner-fully-furnished-nice-santorini-with-3-carparks-115127587.htm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 3d | RM 368,000 | 5% | RM 388,000 | Hillside Garden, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tanjong Bungah Hillside Garden Apartment For Sale.</t>
+          <t>Condominium For Sale | listed 3 days ago | RM 538,000 | I-Santorini, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Single Storey Semi D House Hillside,Tanjung Bungah,Penang.</t>
+          <t>House for sale</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Semi-Detached House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RM 1,650,000</t>
+          <t>RM 760,000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2127,7 +2307,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2137,46 +2317,52 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/single-storey-semi-d-house-hillside-tanjung-bungah-penang-113480651.htm</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>https://www.mudah.my/house-for-sale-108064933.htm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Semi-Detached House For Sale | 3d | RM 1,650,000 | Tanjung Bungah, Penang |  | 4,395 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Single Storey Semi D House Hillside,Tanjung Bungah,Penang.</t>
+          <t>Townhouse For Sale | listed 3 days ago | RM 760,000 | Tanjung Bungah, Penang |  | 1,200 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | House for sale</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Apartment For Sale</t>
+          <t>Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RM 180,000</t>
+          <t>RM 353,800</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Puncak Erskine, Tanjong Tokong</t>
+          <t>Tri Pinnacle, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2186,56 +2372,62 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>650</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/apartment-for-sale-115093031.htm</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>https://www.mudah.my/tg-tokong-apartment-fully-furnished-with-2-carparks-115129412.htm</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Apartment For Sale | 4d | RM 180,000 | Puncak Erskine, Tanjong Tokong |  | 600 |  | sq.ft |  | 3 |  | Bed |  | 1 |  | Bath |  | Freehold |  | Apartment For Sale</t>
+          <t>Condominium For Sale | listed 3 days ago | RM 353,800 | Tri Pinnacle, Tanjong Tokong |  | 650 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Tg Tokong Apartment - Fully Furnished with 2 carparks</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>E Garden apartment for sale</t>
+          <t>Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RM 342,000</t>
+          <t>RM 1,200,000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>E Garden, Tanjong Tokong</t>
+          <t>Quayside, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2245,31 +2437,37 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/e-garden-apartment-for-sale-115127752.htm</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>https://www.mudah.my/pinang-quayside-condo-fully-furnished-1bedroom-2-bathrooms-unit-103758517.htm</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Apartment For Sale | 3d | RM 342,000 | E Garden, Tanjong Tokong |  | 760 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | E Garden apartment for sale</t>
+          <t>Condominium For Sale | listed 2 days ago | RM 1,200,000 | Quayside, Tanjong Tokong |  | 1,137 |  | sq.ft |  | 1 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Pinang Quayside Condo Fully Furnished 1Bedroom 2 Bathrooms Unit</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
+          <t>Marine Mansion</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2279,12 +2477,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RM 538,000</t>
+          <t>RM 600,000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>I-Santorini, Tanjong Tokong</t>
+          <t>Marine Mansion, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2304,41 +2502,47 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/direct-owner-fully-furnished-nice-santorini-with-3-carparks-115127587.htm</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>https://www.mudah.my/marine-mansion-115137839.htm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 3d | RM 538,000 | I-Santorini, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Leasehold |  | Direct Owner Fully Furnished Nice Santorini with 3 carparks</t>
+          <t>Condominium For Sale | listed 2 days ago | RM 600,000 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Marine Mansion</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
+          <t>Azuria Condominium - Direct Owner</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1-storey Terraced House</t>
+          <t>Condominium</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RM 410,000</t>
+          <t>RM 335,000</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tanjong Tokong, Penang</t>
+          <t>Azuria, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2353,46 +2557,52 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>700</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/taman-intan-delima-single-storey-terrace-batu-kawan-freehold-115126865.htm</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>https://www.mudah.my/azuria-condominium-direct-owner-111620926.htm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1-storey Terraced House For Sale | 3d | RM 410,000 | Tanjong Tokong, Penang |  | 1,000 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TAMAN INTAN DELIMA SINGLE STOREY TERRACE @ BATU KAWAN Freehold</t>
+          <t>Condominium For Sale | listed 1 day ago | RM 335,000 | Azuria, Tanjung Bungah |  | 700 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Azuria Condominium - Direct Owner</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>House for sale</t>
+          <t>[RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RM 760,000</t>
+          <t>RM 360,000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tanjung Bungah, Penang</t>
+          <t>Skyridge Apartment, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2407,31 +2617,37 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>750</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/house-for-sale-108064933.htm</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>https://www.mudah.my/rare-unit-skyridge-apartment-for-sales-tanjong-tokong-gurney-115113858.htm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Townhouse For Sale | 3d | RM 760,000 | Tanjung Bungah, Penang |  | 1,200 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | House for sale</t>
+          <t>Apartment For Sale | listed 1 day ago | RM 360,000 | Skyridge Apartment, Tanjong Tokong |  | 750 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | [RARE UNIT] Skyridge Apartment for Sales Tanjong Tokong Gurney</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>The Peak Condominium</t>
+          <t>Andaman</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2441,12 +2657,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RM 530,000</t>
+          <t>RM 4,000,000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>The Peak Residences, Tanjong Tokong</t>
+          <t>18 East @ Andaman, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2456,36 +2672,42 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-peak-condominium-115093455.htm</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>https://www.mudah.my/andaman-115157424.htm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 4d | RM 530,000 | The Peak Residences, Tanjong Tokong |  | 1,100 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The Peak Condominium</t>
+          <t>Condominium For Sale | listed 2 hours ago | RM 4,000,000 | 18 East @ Andaman, Tanjong Tokong |  | 2,827 |  | sq.ft |  | 3 |  | Bed |  | 3 |  | Bath |  | Freehold |  | Andaman</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
+          <t>city of dream condominiums house gurney sea view</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2495,17 +2717,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RM 500,000</t>
+          <t>RM 15,933,500</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>City Of Dreams, Tanjong Tokong</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2515,31 +2737,37 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-tanjung-tokong-jalan-persiaran-halia-3-tanjung-tokong-115090201.htm</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>https://www.mudah.my/city-of-dream-condominiums-house-gurney-sea-view-115155857.htm</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 4d | RM 500,000 | Tri Pinnacle, Tanjong Tokong |  | 850 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI PINNACLE, Tanjung Tokong Jalan Persiaran Halia 3, Tanjung Tokong,</t>
+          <t>Condominium For Sale | listed 5 hours ago | RM 15,933,500 | City Of Dreams, Tanjong Tokong |  | 1,500 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | city of dream condominiums house gurney sea view</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>The peak RENO to TWO room</t>
+          <t>Looking For Investors Only</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2549,17 +2777,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RM 528,000</t>
+          <t>RM 598,888</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>The Peak Residences, Tanjong Tokong</t>
+          <t>Marine Mansion, Tanjung Bungah</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2569,31 +2797,37 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>850</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/the-peak-reno-to-two-room-115092789.htm</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>https://www.mudah.my/looking-for-investors-only-115155444.htm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 4d | RM 528,000 | The Peak Residences, Tanjong Tokong |  | 1,000 |  | sq.ft |  | 2 |  | Bed |  | 2 |  | Bath |  | Freehold |  | The peak RENO to TWO room</t>
+          <t>Condominium For Sale | listed 5 hours ago | RM 598,888 | Marine Mansion, Tanjung Bungah |  | 850 |  | sq.ft |  | 4 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TRI Pinnacle</t>
+          <t>Looking For Investors Only</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2603,17 +2837,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RM 550,000</t>
+          <t>RM 888,888</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tri Pinnacle, Tanjong Tokong</t>
+          <t>Desa Mas (Pulau Tikus), Pulau Tikus</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2623,24 +2857,30 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.mudah.my/tri-pinnacle-114681845.htm</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>https://www.mudah.my/looking-for-investors-only-115155435.htm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Condominium For Sale | 2w | RM 550,000 | Tri Pinnacle, Tanjong Tokong |  | 800 |  | sq.ft |  | 3 |  | Bed |  | 2 |  | Bath |  | Freehold |  | TRI Pinnacle</t>
+          <t>Condominium For Sale | listed 5 hours ago | RM 888,888 | Desa Mas (Pulau Tikus), Pulau Tikus |  | 1,089 |  | sq.ft |  | 5 |  | Bed |  | 2 |  | Bath |  | Freehold |  | Looking For Investors Only</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-07-02 08:35</t>
+          <t>2026-07-02 08:57</t>
         </is>
       </c>
     </row>
